--- a/research/traditional_assets/database/data/taiwan/taiwan_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/taiwan/taiwan_hospitals_healthcare_facilities.xlsx
@@ -1266,7 +1266,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1403,22 +1403,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07477993657632225</v>
+        <v>0.0746663767031696</v>
       </c>
       <c r="C2">
-        <v>213.591312815303</v>
+        <v>212.2609217798002</v>
       </c>
       <c r="D2">
-        <v>206.561312815303</v>
+        <v>207.3739217798002</v>
       </c>
       <c r="E2">
-        <v>-35</v>
+        <v>-32.857</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2.143</v>
       </c>
       <c r="G2">
         <v>7.03</v>
@@ -1439,28 +1439,28 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.1077929</v>
       </c>
       <c r="N2">
-        <v>2.734999999999999</v>
+        <v>2.627207099999999</v>
       </c>
       <c r="O2">
-        <v>0.5469999999999999</v>
+        <v>0.5254414199999998</v>
       </c>
       <c r="P2">
-        <v>2.188</v>
+        <v>2.101765679999999</v>
       </c>
       <c r="Q2">
-        <v>4.128</v>
+        <v>4.041765679999999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07477993657632225</v>
+        <v>0.0750141178819895</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5694375337289941</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1477,7 +1477,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>25.37272863054987</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1485,22 +1485,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.0746663767031696</v>
+        <v>0.07457681683001696</v>
       </c>
       <c r="C3">
-        <v>212.2609217798002</v>
+        <v>210.7633156827975</v>
       </c>
       <c r="D3">
-        <v>207.3739217798002</v>
+        <v>208.0193156827975</v>
       </c>
       <c r="E3">
-        <v>-32.857</v>
+        <v>-30.714</v>
       </c>
       <c r="F3">
-        <v>2.143</v>
+        <v>4.286</v>
       </c>
       <c r="G3">
         <v>7.03</v>
@@ -1521,45 +1521,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M3">
-        <v>0.1077929</v>
+        <v>0.2220148</v>
       </c>
       <c r="N3">
-        <v>2.627207099999999</v>
+        <v>2.512985199999999</v>
       </c>
       <c r="O3">
-        <v>0.5254414199999998</v>
+        <v>0.5025970399999998</v>
       </c>
       <c r="P3">
-        <v>2.101765679999999</v>
+        <v>2.010388159999999</v>
       </c>
       <c r="Q3">
-        <v>4.041765679999999</v>
+        <v>3.950388159999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0750141178819895</v>
+        <v>0.07525307839797649</v>
       </c>
       <c r="T3">
-        <v>0.5694375337289941</v>
+        <v>0.5740953189625549</v>
       </c>
       <c r="U3">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V3">
         <v>0.2</v>
       </c>
       <c r="W3">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y3">
-        <v>25.37272863054987</v>
+        <v>12.3189985532496</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1567,22 +1567,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07457681683001696</v>
+        <v>0.07451605695686429</v>
       </c>
       <c r="C4">
-        <v>210.7633156827975</v>
+        <v>209.0604606251612</v>
       </c>
       <c r="D4">
-        <v>208.0193156827975</v>
+        <v>208.4594606251612</v>
       </c>
       <c r="E4">
-        <v>-30.714</v>
+        <v>-28.571</v>
       </c>
       <c r="F4">
-        <v>4.286</v>
+        <v>6.429</v>
       </c>
       <c r="G4">
         <v>7.03</v>
@@ -1603,45 +1603,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M4">
-        <v>0.2220148</v>
+        <v>0.3439515</v>
       </c>
       <c r="N4">
-        <v>2.512985199999999</v>
+        <v>2.391048499999999</v>
       </c>
       <c r="O4">
-        <v>0.5025970399999998</v>
+        <v>0.4782096999999998</v>
       </c>
       <c r="P4">
-        <v>2.010388159999999</v>
+        <v>1.912838799999999</v>
       </c>
       <c r="Q4">
-        <v>3.950388159999999</v>
+        <v>3.8528388</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.07525307839797649</v>
+        <v>0.07549696593491165</v>
       </c>
       <c r="T4">
-        <v>0.5740953189625549</v>
+        <v>0.5788491410050552</v>
       </c>
       <c r="U4">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V4">
         <v>0.2</v>
       </c>
       <c r="W4">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y4">
-        <v>12.3189985532496</v>
+        <v>7.951702492938682</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1649,22 +1649,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07451605695686429</v>
+        <v>0.07448569708371167</v>
       </c>
       <c r="C5">
-        <v>209.0604606251612</v>
+        <v>207.1380863524558</v>
       </c>
       <c r="D5">
-        <v>208.4594606251612</v>
+        <v>208.6800863524558</v>
       </c>
       <c r="E5">
-        <v>-28.571</v>
+        <v>-26.428</v>
       </c>
       <c r="F5">
-        <v>6.429</v>
+        <v>8.572000000000001</v>
       </c>
       <c r="G5">
         <v>7.03</v>
@@ -1685,45 +1685,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M5">
-        <v>0.3439515</v>
+        <v>0.4740316000000001</v>
       </c>
       <c r="N5">
-        <v>2.391048499999999</v>
+        <v>2.260968399999999</v>
       </c>
       <c r="O5">
-        <v>0.4782096999999998</v>
+        <v>0.4521936799999999</v>
       </c>
       <c r="P5">
-        <v>1.912838799999999</v>
+        <v>1.80877472</v>
       </c>
       <c r="Q5">
-        <v>3.8528388</v>
+        <v>3.74877472</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07549696593491165</v>
+        <v>0.07574593446219965</v>
       </c>
       <c r="T5">
-        <v>0.5788491410050552</v>
+        <v>0.5837020010067745</v>
       </c>
       <c r="U5">
-        <v>0.0535</v>
+        <v>0.0553</v>
       </c>
       <c r="V5">
         <v>0.2</v>
       </c>
       <c r="W5">
-        <v>0.0428</v>
+        <v>0.04424</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y5">
-        <v>7.951702492938682</v>
+        <v>5.769657550256142</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1731,22 +1731,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07448569708371167</v>
+        <v>0.074412137210559</v>
       </c>
       <c r="C6">
-        <v>207.1380863524558</v>
+        <v>205.5315887664002</v>
       </c>
       <c r="D6">
-        <v>208.6800863524558</v>
+        <v>209.2165887664002</v>
       </c>
       <c r="E6">
-        <v>-26.428</v>
+        <v>-24.285</v>
       </c>
       <c r="F6">
-        <v>8.572000000000001</v>
+        <v>10.715</v>
       </c>
       <c r="G6">
         <v>7.03</v>
@@ -1767,28 +1767,28 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M6">
-        <v>0.4740316000000001</v>
+        <v>0.5925395000000001</v>
       </c>
       <c r="N6">
-        <v>2.260968399999999</v>
+        <v>2.142460499999999</v>
       </c>
       <c r="O6">
-        <v>0.4521936799999999</v>
+        <v>0.4284920999999999</v>
       </c>
       <c r="P6">
-        <v>1.80877472</v>
+        <v>1.7139684</v>
       </c>
       <c r="Q6">
-        <v>3.74877472</v>
+        <v>3.6539684</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07574593446219965</v>
+        <v>0.07600014443216738</v>
       </c>
       <c r="T6">
-        <v>0.5837020010067745</v>
+        <v>0.5886570264822139</v>
       </c>
       <c r="U6">
         <v>0.0553</v>
@@ -1805,7 +1805,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>5.769657550256142</v>
+        <v>4.615726040204914</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1813,22 +1813,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.074412137210559</v>
+        <v>0.07476097733740639</v>
       </c>
       <c r="C7">
-        <v>205.5315887664002</v>
+        <v>200.8685377158584</v>
       </c>
       <c r="D7">
-        <v>209.2165887664002</v>
+        <v>206.6965377158584</v>
       </c>
       <c r="E7">
-        <v>-24.285</v>
+        <v>-22.142</v>
       </c>
       <c r="F7">
-        <v>10.715</v>
+        <v>12.858</v>
       </c>
       <c r="G7">
         <v>7.03</v>
@@ -1849,45 +1849,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M7">
-        <v>0.5925395000000001</v>
+        <v>0.8241978000000002</v>
       </c>
       <c r="N7">
-        <v>2.142460499999999</v>
+        <v>1.910802199999999</v>
       </c>
       <c r="O7">
-        <v>0.4284920999999999</v>
+        <v>0.3821604399999998</v>
       </c>
       <c r="P7">
-        <v>1.7139684</v>
+        <v>1.528641759999999</v>
       </c>
       <c r="Q7">
-        <v>3.6539684</v>
+        <v>3.46864176</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07600014443216738</v>
+        <v>0.0762597631249004</v>
       </c>
       <c r="T7">
-        <v>0.5886570264822139</v>
+        <v>0.593717478031599</v>
       </c>
       <c r="U7">
-        <v>0.0553</v>
+        <v>0.0641</v>
       </c>
       <c r="V7">
         <v>0.2</v>
       </c>
       <c r="W7">
-        <v>0.04424</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y7">
-        <v>4.615726040204914</v>
+        <v>3.318378185430729</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1895,22 +1895,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07476097733740639</v>
+        <v>0.07519461746425374</v>
       </c>
       <c r="C8">
-        <v>200.8685377158584</v>
+        <v>195.6762749403515</v>
       </c>
       <c r="D8">
-        <v>206.6965377158584</v>
+        <v>203.6472749403515</v>
       </c>
       <c r="E8">
-        <v>-22.142</v>
+        <v>-19.999</v>
       </c>
       <c r="F8">
-        <v>12.858</v>
+        <v>15.001</v>
       </c>
       <c r="G8">
         <v>7.03</v>
@@ -1931,45 +1931,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M8">
-        <v>0.8241978000000001</v>
+        <v>1.0785719</v>
       </c>
       <c r="N8">
-        <v>1.910802199999999</v>
+        <v>1.656428099999999</v>
       </c>
       <c r="O8">
-        <v>0.3821604399999999</v>
+        <v>0.3312856199999999</v>
       </c>
       <c r="P8">
-        <v>1.52864176</v>
+        <v>1.32514248</v>
       </c>
       <c r="Q8">
-        <v>3.46864176</v>
+        <v>3.26514248</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.0762597631249004</v>
+        <v>0.0765249650153266</v>
       </c>
       <c r="T8">
-        <v>0.593717478031599</v>
+        <v>0.5988867564960246</v>
       </c>
       <c r="U8">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V8">
         <v>0.2</v>
       </c>
       <c r="W8">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y8">
-        <v>3.318378185430729</v>
+        <v>2.535760481058333</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07519461746425374</v>
+        <v>0.07550345759110109</v>
       </c>
       <c r="C9">
-        <v>195.6762749403515</v>
+        <v>191.4158631867939</v>
       </c>
       <c r="D9">
-        <v>203.6472749403515</v>
+        <v>201.5298631867939</v>
       </c>
       <c r="E9">
-        <v>-19.999</v>
+        <v>-17.856</v>
       </c>
       <c r="F9">
-        <v>15.001</v>
+        <v>17.144</v>
       </c>
       <c r="G9">
         <v>7.03</v>
@@ -2013,45 +2013,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M9">
-        <v>1.0785719</v>
+        <v>1.2995152</v>
       </c>
       <c r="N9">
-        <v>1.656428099999999</v>
+        <v>1.435484799999999</v>
       </c>
       <c r="O9">
-        <v>0.3312856199999998</v>
+        <v>0.2870969599999998</v>
       </c>
       <c r="P9">
-        <v>1.325142479999999</v>
+        <v>1.148387839999999</v>
       </c>
       <c r="Q9">
-        <v>3.26514248</v>
+        <v>3.088387839999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.0765249650153266</v>
+        <v>0.07679593216424031</v>
       </c>
       <c r="T9">
-        <v>0.5988867564960246</v>
+        <v>0.604168410579242</v>
       </c>
       <c r="U9">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V9">
         <v>0.2</v>
       </c>
       <c r="W9">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y9">
-        <v>2.535760481058332</v>
+        <v>2.104631019321666</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2059,22 +2059,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07550345759110109</v>
+        <v>0.07661629771794844</v>
       </c>
       <c r="C10">
-        <v>191.4158631867939</v>
+        <v>181.9952037948386</v>
       </c>
       <c r="D10">
-        <v>201.5298631867939</v>
+        <v>194.2522037948386</v>
       </c>
       <c r="E10">
-        <v>-17.856</v>
+        <v>-15.713</v>
       </c>
       <c r="F10">
-        <v>17.144</v>
+        <v>19.287</v>
       </c>
       <c r="G10">
         <v>7.03</v>
@@ -2095,45 +2095,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M10">
-        <v>1.2995152</v>
+        <v>1.73583</v>
       </c>
       <c r="N10">
-        <v>1.435484799999999</v>
+        <v>0.9991699999999997</v>
       </c>
       <c r="O10">
-        <v>0.2870969599999998</v>
+        <v>0.199834</v>
       </c>
       <c r="P10">
-        <v>1.148387839999999</v>
+        <v>0.7993359999999997</v>
       </c>
       <c r="Q10">
-        <v>3.088387839999999</v>
+        <v>2.739336</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07679593216424031</v>
+        <v>0.07707285463510817</v>
       </c>
       <c r="T10">
-        <v>0.604168410579242</v>
+        <v>0.6095661449719806</v>
       </c>
       <c r="U10">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V10">
         <v>0.2</v>
       </c>
       <c r="W10">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y10">
-        <v>2.104631019321666</v>
+        <v>1.575615123600813</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2141,22 +2141,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07661629771794844</v>
+        <v>0.08182354915859541</v>
       </c>
       <c r="C11">
-        <v>181.9952037948386</v>
+        <v>151.7727920853966</v>
       </c>
       <c r="D11">
-        <v>194.2522037948386</v>
+        <v>166.1727920853966</v>
       </c>
       <c r="E11">
-        <v>-15.713</v>
+        <v>-13.57</v>
       </c>
       <c r="F11">
-        <v>19.287</v>
+        <v>21.43</v>
       </c>
       <c r="G11">
         <v>7.03</v>
@@ -2177,45 +2177,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M11">
-        <v>1.73583</v>
+        <v>3.145924</v>
       </c>
       <c r="N11">
-        <v>0.9991699999999997</v>
+        <v>-0.410924000000001</v>
       </c>
       <c r="O11">
-        <v>0.199834</v>
+        <v>-0.0821848000000002</v>
       </c>
       <c r="P11">
-        <v>0.7993359999999997</v>
+        <v>-0.3287392000000008</v>
       </c>
       <c r="Q11">
-        <v>2.739336</v>
+        <v>1.611260799999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07707285463510817</v>
+        <v>0.07744005073203192</v>
       </c>
       <c r="T11">
-        <v>0.6095661449719806</v>
+        <v>0.6167234803627604</v>
       </c>
       <c r="U11">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V11">
-        <v>0.2</v>
+        <v>0.1738757833946401</v>
       </c>
       <c r="W11">
-        <v>0.07199999999999999</v>
+        <v>0.1212750349976668</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y11">
-        <v>1.575615123600813</v>
+        <v>0.8693789169732006</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2223,22 +2223,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08182354915859541</v>
+        <v>0.08890905767226399</v>
       </c>
       <c r="C12">
-        <v>151.7727920853966</v>
+        <v>122.3172318802428</v>
       </c>
       <c r="D12">
-        <v>166.1727920853966</v>
+        <v>138.8602318802428</v>
       </c>
       <c r="E12">
-        <v>-13.57</v>
+        <v>-11.427</v>
       </c>
       <c r="F12">
-        <v>21.43</v>
+        <v>23.573</v>
       </c>
       <c r="G12">
         <v>7.03</v>
@@ -2259,45 +2259,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M12">
-        <v>3.145924000000001</v>
+        <v>4.7334584</v>
       </c>
       <c r="N12">
-        <v>-0.4109240000000014</v>
+        <v>-1.998458400000001</v>
       </c>
       <c r="O12">
-        <v>-0.08218480000000028</v>
+        <v>-0.3996916800000001</v>
       </c>
       <c r="P12">
-        <v>-0.3287392000000011</v>
+        <v>-1.59876672</v>
       </c>
       <c r="Q12">
-        <v>1.611260799999999</v>
+        <v>0.3412332799999998</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07744005073203192</v>
+        <v>0.07794781367696327</v>
       </c>
       <c r="T12">
-        <v>0.6167234803627604</v>
+        <v>0.6266207252581446</v>
       </c>
       <c r="U12">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V12">
-        <v>0.1738757833946401</v>
+        <v>0.115560326884884</v>
       </c>
       <c r="W12">
-        <v>0.1212750349976669</v>
+        <v>0.1775954863615153</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y12">
-        <v>0.8693789169732005</v>
+        <v>0.5778016344244199</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2305,22 +2305,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08890905767226399</v>
+        <v>0.09045905767226399</v>
       </c>
       <c r="C13">
-        <v>122.3172318802428</v>
+        <v>115.3547535787997</v>
       </c>
       <c r="D13">
-        <v>138.8602318802428</v>
+        <v>134.0407535787997</v>
       </c>
       <c r="E13">
-        <v>-11.427</v>
+        <v>-9.283999999999999</v>
       </c>
       <c r="F13">
-        <v>23.573</v>
+        <v>25.716</v>
       </c>
       <c r="G13">
         <v>7.03</v>
@@ -2341,37 +2341,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M13">
-        <v>4.7334584</v>
+        <v>5.1637728</v>
       </c>
       <c r="N13">
-        <v>-1.998458400000001</v>
+        <v>-2.428772800000001</v>
       </c>
       <c r="O13">
-        <v>-0.3996916800000001</v>
+        <v>-0.4857545600000002</v>
       </c>
       <c r="P13">
-        <v>-1.59876672</v>
+        <v>-1.943018240000001</v>
       </c>
       <c r="Q13">
-        <v>0.3412332799999998</v>
+        <v>-0.003018240000000505</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07794781367696327</v>
+        <v>0.07831312974147422</v>
       </c>
       <c r="T13">
-        <v>0.6266207252581446</v>
+        <v>0.6337414153178963</v>
       </c>
       <c r="U13">
         <v>0.2008</v>
       </c>
       <c r="V13">
-        <v>0.115560326884884</v>
+        <v>0.105930299644477</v>
       </c>
       <c r="W13">
-        <v>0.1775954863615153</v>
+        <v>0.179529195831389</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>0.5778016344244199</v>
+        <v>0.5296514982223849</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2387,22 +2387,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09045905767226399</v>
+        <v>0.0966137369942906</v>
       </c>
       <c r="C14">
-        <v>115.3547535787997</v>
+        <v>96.9764222853544</v>
       </c>
       <c r="D14">
-        <v>134.0407535787997</v>
+        <v>117.8054222853544</v>
       </c>
       <c r="E14">
-        <v>-9.283999999999999</v>
+        <v>-7.140999999999998</v>
       </c>
       <c r="F14">
-        <v>25.716</v>
+        <v>27.859</v>
       </c>
       <c r="G14">
         <v>7.03</v>
@@ -2423,45 +2423,45 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M14">
-        <v>5.1637728</v>
+        <v>6.5691522</v>
       </c>
       <c r="N14">
-        <v>-2.428772800000001</v>
+        <v>-3.834152200000001</v>
       </c>
       <c r="O14">
-        <v>-0.4857545600000002</v>
+        <v>-0.7668304400000002</v>
       </c>
       <c r="P14">
-        <v>-1.943018240000001</v>
+        <v>-3.067321760000001</v>
       </c>
       <c r="Q14">
-        <v>-0.003018240000000505</v>
+        <v>-1.127321760000001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.07831312974147422</v>
+        <v>0.07874969367186657</v>
       </c>
       <c r="T14">
-        <v>0.6337414153178963</v>
+        <v>0.6422508588972595</v>
       </c>
       <c r="U14">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V14">
-        <v>0.105930299644477</v>
+        <v>0.08326797482329606</v>
       </c>
       <c r="W14">
-        <v>0.179529195831389</v>
+        <v>0.2161654115366668</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y14">
-        <v>0.5296514982223849</v>
+        <v>0.4163398741164802</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2469,22 +2469,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.0966137369942906</v>
+        <v>0.09851373699429058</v>
       </c>
       <c r="C15">
-        <v>96.9764222853544</v>
+        <v>90.58727478937219</v>
       </c>
       <c r="D15">
-        <v>117.8054222853544</v>
+        <v>113.5592747893722</v>
       </c>
       <c r="E15">
-        <v>-7.140999999999998</v>
+        <v>-4.997999999999994</v>
       </c>
       <c r="F15">
-        <v>27.859</v>
+        <v>30.00200000000001</v>
       </c>
       <c r="G15">
         <v>7.03</v>
@@ -2505,37 +2505,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M15">
-        <v>6.5691522</v>
+        <v>7.074471600000002</v>
       </c>
       <c r="N15">
-        <v>-3.834152200000001</v>
+        <v>-4.339471600000002</v>
       </c>
       <c r="O15">
-        <v>-0.7668304400000002</v>
+        <v>-0.8678943200000004</v>
       </c>
       <c r="P15">
-        <v>-3.067321760000001</v>
+        <v>-3.471577280000002</v>
       </c>
       <c r="Q15">
-        <v>-1.127321760000001</v>
+        <v>-1.531577280000002</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.07874969367186657</v>
+        <v>0.07913282964479523</v>
       </c>
       <c r="T15">
-        <v>0.6422508588972595</v>
+        <v>0.6497188921402508</v>
       </c>
       <c r="U15">
         <v>0.2358</v>
       </c>
       <c r="V15">
-        <v>0.08326797482329606</v>
+        <v>0.07732026233591775</v>
       </c>
       <c r="W15">
-        <v>0.2161654115366668</v>
+        <v>0.2175678821411906</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
@@ -2543,7 +2543,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>0.4163398741164802</v>
+        <v>0.3866013116795888</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2551,22 +2551,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09851373699429058</v>
+        <v>0.1004137369942906</v>
       </c>
       <c r="C16">
-        <v>90.58727478937219</v>
+        <v>84.49357238418128</v>
       </c>
       <c r="D16">
-        <v>113.5592747893722</v>
+        <v>109.6085723841813</v>
       </c>
       <c r="E16">
-        <v>-4.997999999999994</v>
+        <v>-2.854999999999997</v>
       </c>
       <c r="F16">
-        <v>30.00200000000001</v>
+        <v>32.145</v>
       </c>
       <c r="G16">
         <v>7.03</v>
@@ -2587,37 +2587,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M16">
-        <v>7.074471600000002</v>
+        <v>7.579791000000001</v>
       </c>
       <c r="N16">
-        <v>-4.339471600000002</v>
+        <v>-4.844791000000002</v>
       </c>
       <c r="O16">
-        <v>-0.8678943200000004</v>
+        <v>-0.9689582000000003</v>
       </c>
       <c r="P16">
-        <v>-3.471577280000002</v>
+        <v>-3.875832800000001</v>
       </c>
       <c r="Q16">
-        <v>-1.531577280000002</v>
+        <v>-1.935832800000001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.07913282964479523</v>
+        <v>0.07952498058179283</v>
       </c>
       <c r="T16">
-        <v>0.6497188921402508</v>
+        <v>0.6573626438124891</v>
       </c>
       <c r="U16">
         <v>0.2358</v>
       </c>
       <c r="V16">
-        <v>0.07732026233591775</v>
+        <v>0.07216557818018991</v>
       </c>
       <c r="W16">
-        <v>0.2175678821411906</v>
+        <v>0.2187833566651112</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>0.3866013116795888</v>
+        <v>0.3608278909009495</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2633,22 +2633,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1004137369942906</v>
+        <v>0.1023137369942906</v>
       </c>
       <c r="C17">
-        <v>84.49357238418128</v>
+        <v>78.66551634991154</v>
       </c>
       <c r="D17">
-        <v>109.6085723841813</v>
+        <v>105.9235163499115</v>
       </c>
       <c r="E17">
-        <v>-2.854999999999997</v>
+        <v>-0.7119999999999962</v>
       </c>
       <c r="F17">
-        <v>32.145</v>
+        <v>34.288</v>
       </c>
       <c r="G17">
         <v>7.03</v>
@@ -2669,37 +2669,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M17">
-        <v>7.579791000000001</v>
+        <v>8.085110400000001</v>
       </c>
       <c r="N17">
-        <v>-4.844791000000002</v>
+        <v>-5.350110400000002</v>
       </c>
       <c r="O17">
-        <v>-0.9689582000000003</v>
+        <v>-1.07002208</v>
       </c>
       <c r="P17">
-        <v>-3.875832800000001</v>
+        <v>-4.280088320000002</v>
       </c>
       <c r="Q17">
-        <v>-1.935832800000001</v>
+        <v>-2.340088320000001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.07952498058179283</v>
+        <v>0.07992646844586179</v>
       </c>
       <c r="T17">
-        <v>0.6573626438124891</v>
+        <v>0.6651883895721616</v>
       </c>
       <c r="U17">
         <v>0.2358</v>
       </c>
       <c r="V17">
-        <v>0.07216557818018991</v>
+        <v>0.06765522954392804</v>
       </c>
       <c r="W17">
-        <v>0.2187833566651112</v>
+        <v>0.2198468968735418</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>0.3608278909009495</v>
+        <v>0.3382761477196402</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2715,22 +2715,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1023137369942906</v>
+        <v>0.1042137369942906</v>
       </c>
       <c r="C18">
-        <v>78.66551634991154</v>
+        <v>73.07718497033375</v>
       </c>
       <c r="D18">
-        <v>105.9235163499115</v>
+        <v>102.4781849703337</v>
       </c>
       <c r="E18">
-        <v>-0.7119999999999962</v>
+        <v>1.431000000000004</v>
       </c>
       <c r="F18">
-        <v>34.288</v>
+        <v>36.431</v>
       </c>
       <c r="G18">
         <v>7.03</v>
@@ -2751,37 +2751,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M18">
-        <v>8.085110400000001</v>
+        <v>8.590429800000001</v>
       </c>
       <c r="N18">
-        <v>-5.350110400000002</v>
+        <v>-5.855429800000001</v>
       </c>
       <c r="O18">
-        <v>-1.07002208</v>
+        <v>-1.17108596</v>
       </c>
       <c r="P18">
-        <v>-4.280088320000002</v>
+        <v>-4.684343840000001</v>
       </c>
       <c r="Q18">
-        <v>-2.340088320000001</v>
+        <v>-2.744343840000001</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.07992646844586179</v>
+        <v>0.08033763071629386</v>
       </c>
       <c r="T18">
-        <v>0.6651883895721616</v>
+        <v>0.6732027075188141</v>
       </c>
       <c r="U18">
         <v>0.2358</v>
       </c>
       <c r="V18">
-        <v>0.06765522954392804</v>
+        <v>0.0636755101589911</v>
       </c>
       <c r="W18">
-        <v>0.2198468968735418</v>
+        <v>0.2207853147045099</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
@@ -2789,7 +2789,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>0.3382761477196402</v>
+        <v>0.3183775507949554</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2797,22 +2797,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1042137369942906</v>
+        <v>0.1061137369942906</v>
       </c>
       <c r="C19">
-        <v>73.07718497033375</v>
+        <v>67.70592286709072</v>
       </c>
       <c r="D19">
-        <v>102.4781849703337</v>
+        <v>99.24992286709072</v>
       </c>
       <c r="E19">
-        <v>1.431000000000004</v>
+        <v>3.574000000000005</v>
       </c>
       <c r="F19">
-        <v>36.431</v>
+        <v>38.57400000000001</v>
       </c>
       <c r="G19">
         <v>7.03</v>
@@ -2833,37 +2833,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M19">
-        <v>8.590429800000001</v>
+        <v>9.095749200000002</v>
       </c>
       <c r="N19">
-        <v>-5.855429800000001</v>
+        <v>-6.360749200000003</v>
       </c>
       <c r="O19">
-        <v>-1.17108596</v>
+        <v>-1.272149840000001</v>
       </c>
       <c r="P19">
-        <v>-4.684343840000001</v>
+        <v>-5.088599360000002</v>
       </c>
       <c r="Q19">
-        <v>-2.744343840000001</v>
+        <v>-3.148599360000001</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08033763071629386</v>
+        <v>0.08075882133478526</v>
       </c>
       <c r="T19">
-        <v>0.6732027075188141</v>
+        <v>0.6814124966348973</v>
       </c>
       <c r="U19">
         <v>0.2358</v>
       </c>
       <c r="V19">
-        <v>0.0636755101589911</v>
+        <v>0.06013798181682492</v>
       </c>
       <c r="W19">
-        <v>0.2207853147045099</v>
+        <v>0.2216194638875927</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
@@ -2871,7 +2871,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>0.3183775507949554</v>
+        <v>0.3006899090841246</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2879,22 +2879,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1061137369942906</v>
+        <v>0.1080137369942906</v>
       </c>
       <c r="C20">
-        <v>67.70592286709072</v>
+        <v>62.53184223188021</v>
       </c>
       <c r="D20">
-        <v>99.24992286709072</v>
+        <v>96.21884223188022</v>
       </c>
       <c r="E20">
-        <v>3.573999999999998</v>
+        <v>5.717000000000006</v>
       </c>
       <c r="F20">
-        <v>38.574</v>
+        <v>40.71700000000001</v>
       </c>
       <c r="G20">
         <v>7.03</v>
@@ -2915,37 +2915,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M20">
-        <v>9.0957492</v>
+        <v>9.601068600000001</v>
       </c>
       <c r="N20">
-        <v>-6.360749200000001</v>
+        <v>-6.866068600000002</v>
       </c>
       <c r="O20">
-        <v>-1.27214984</v>
+        <v>-1.373213720000001</v>
       </c>
       <c r="P20">
-        <v>-5.088599360000001</v>
+        <v>-5.492854880000001</v>
       </c>
       <c r="Q20">
-        <v>-3.14859936</v>
+        <v>-3.552854880000001</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.08075882133478526</v>
+        <v>0.08119041172163446</v>
       </c>
       <c r="T20">
-        <v>0.6814124966348972</v>
+        <v>0.6898249965933527</v>
       </c>
       <c r="U20">
         <v>0.2358</v>
       </c>
       <c r="V20">
-        <v>0.06013798181682493</v>
+        <v>0.0569728248790973</v>
       </c>
       <c r="W20">
-        <v>0.2216194638875927</v>
+        <v>0.2223658078935089</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>0.3006899090841246</v>
+        <v>0.2848641243954865</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2961,22 +2961,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1080137369942906</v>
+        <v>0.1099137369942906</v>
       </c>
       <c r="C21">
-        <v>62.53184223188021</v>
+        <v>57.53741274404904</v>
       </c>
       <c r="D21">
-        <v>96.21884223188022</v>
+        <v>93.36741274404905</v>
       </c>
       <c r="E21">
-        <v>5.717000000000006</v>
+        <v>7.860000000000007</v>
       </c>
       <c r="F21">
-        <v>40.71700000000001</v>
+        <v>42.86000000000001</v>
       </c>
       <c r="G21">
         <v>7.03</v>
@@ -2997,37 +2997,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M21">
-        <v>9.601068600000001</v>
+        <v>10.106388</v>
       </c>
       <c r="N21">
-        <v>-6.866068600000002</v>
+        <v>-7.371388000000003</v>
       </c>
       <c r="O21">
-        <v>-1.373213720000001</v>
+        <v>-1.474277600000001</v>
       </c>
       <c r="P21">
-        <v>-5.492854880000001</v>
+        <v>-5.897110400000003</v>
       </c>
       <c r="Q21">
-        <v>-3.552854880000001</v>
+        <v>-3.957110400000002</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08119041172163446</v>
+        <v>0.08163279186815489</v>
       </c>
       <c r="T21">
-        <v>0.6898249965933527</v>
+        <v>0.6984478090507696</v>
       </c>
       <c r="U21">
         <v>0.2358</v>
       </c>
       <c r="V21">
-        <v>0.0569728248790973</v>
+        <v>0.05412418363514242</v>
       </c>
       <c r="W21">
-        <v>0.2223658078935089</v>
+        <v>0.2230375174988334</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.2848641243954865</v>
+        <v>0.2706209181757121</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1099137369942906</v>
+        <v>0.1118137369942906</v>
       </c>
       <c r="C22">
-        <v>57.53741274404904</v>
+        <v>52.70712230586292</v>
       </c>
       <c r="D22">
-        <v>93.36741274404905</v>
+        <v>90.68012230586292</v>
       </c>
       <c r="E22">
-        <v>7.860000000000007</v>
+        <v>10.00300000000001</v>
       </c>
       <c r="F22">
-        <v>42.86000000000001</v>
+        <v>45.00300000000001</v>
       </c>
       <c r="G22">
         <v>7.03</v>
@@ -3079,37 +3079,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M22">
-        <v>10.106388</v>
+        <v>10.6117074</v>
       </c>
       <c r="N22">
-        <v>-7.371388000000003</v>
+        <v>-7.876707400000003</v>
       </c>
       <c r="O22">
-        <v>-1.474277600000001</v>
+        <v>-1.575341480000001</v>
       </c>
       <c r="P22">
-        <v>-5.897110400000003</v>
+        <v>-6.301365920000002</v>
       </c>
       <c r="Q22">
-        <v>-3.957110400000002</v>
+        <v>-4.361365920000002</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.08163279186815489</v>
+        <v>0.08208637151205558</v>
       </c>
       <c r="T22">
-        <v>0.6984478090507696</v>
+        <v>0.7072889205577414</v>
       </c>
       <c r="U22">
         <v>0.2358</v>
       </c>
       <c r="V22">
-        <v>0.05412418363514242</v>
+        <v>0.0515468415572785</v>
       </c>
       <c r="W22">
-        <v>0.2230375174988334</v>
+        <v>0.2236452547607937</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>0.2706209181757121</v>
+        <v>0.2577342077863926</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3125,22 +3125,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1118137369942906</v>
+        <v>0.1137137369942906</v>
       </c>
       <c r="C23">
-        <v>52.70712230586292</v>
+        <v>48.02719472675436</v>
       </c>
       <c r="D23">
-        <v>90.68012230586292</v>
+        <v>88.14319472675436</v>
       </c>
       <c r="E23">
-        <v>10.003</v>
+        <v>12.146</v>
       </c>
       <c r="F23">
-        <v>45.003</v>
+        <v>47.146</v>
       </c>
       <c r="G23">
         <v>7.03</v>
@@ -3161,37 +3161,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M23">
-        <v>10.6117074</v>
+        <v>11.1170268</v>
       </c>
       <c r="N23">
-        <v>-7.876707400000001</v>
+        <v>-8.382026800000002</v>
       </c>
       <c r="O23">
-        <v>-1.57534148</v>
+        <v>-1.67640536</v>
       </c>
       <c r="P23">
-        <v>-6.30136592</v>
+        <v>-6.705621440000002</v>
       </c>
       <c r="Q23">
-        <v>-4.36136592</v>
+        <v>-4.765621440000001</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08208637151205558</v>
+        <v>0.08255158140323579</v>
       </c>
       <c r="T23">
-        <v>0.7072889205577414</v>
+        <v>0.7163567272315586</v>
       </c>
       <c r="U23">
         <v>0.2358</v>
       </c>
       <c r="V23">
-        <v>0.05154684155727851</v>
+        <v>0.04920380330467494</v>
       </c>
       <c r="W23">
-        <v>0.2236452547607937</v>
+        <v>0.2241977431807577</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.2577342077863926</v>
+        <v>0.2460190165233747</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3207,22 +3207,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1137137369942906</v>
+        <v>0.1156137369942906</v>
       </c>
       <c r="C24">
-        <v>48.02719472675436</v>
+        <v>43.48535350737474</v>
       </c>
       <c r="D24">
-        <v>88.14319472675436</v>
+        <v>85.74435350737474</v>
       </c>
       <c r="E24">
-        <v>12.146</v>
+        <v>14.289</v>
       </c>
       <c r="F24">
-        <v>47.146</v>
+        <v>49.289</v>
       </c>
       <c r="G24">
         <v>7.03</v>
@@ -3243,37 +3243,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M24">
-        <v>11.1170268</v>
+        <v>11.6223462</v>
       </c>
       <c r="N24">
-        <v>-8.382026800000002</v>
+        <v>-8.887346200000001</v>
       </c>
       <c r="O24">
-        <v>-1.67640536</v>
+        <v>-1.77746924</v>
       </c>
       <c r="P24">
-        <v>-6.705621440000002</v>
+        <v>-7.109876960000001</v>
       </c>
       <c r="Q24">
-        <v>-4.765621440000001</v>
+        <v>-5.169876960000001</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08255158140323579</v>
+        <v>0.08302887466821286</v>
       </c>
       <c r="T24">
-        <v>0.7163567272315586</v>
+        <v>0.7256600613514489</v>
       </c>
       <c r="U24">
         <v>0.2358</v>
       </c>
       <c r="V24">
-        <v>0.04920380330467494</v>
+        <v>0.04706450750881951</v>
       </c>
       <c r="W24">
-        <v>0.2241977431807577</v>
+        <v>0.2247021891294204</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.2460190165233747</v>
+        <v>0.2353225375440975</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3289,22 +3289,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1156137369942906</v>
+        <v>0.1175137369942906</v>
       </c>
       <c r="C25">
-        <v>43.48535350737474</v>
+        <v>39.07062317379884</v>
       </c>
       <c r="D25">
-        <v>85.74435350737474</v>
+        <v>83.47262317379885</v>
       </c>
       <c r="E25">
-        <v>14.289</v>
+        <v>16.43200000000001</v>
       </c>
       <c r="F25">
-        <v>49.289</v>
+        <v>51.43200000000001</v>
       </c>
       <c r="G25">
         <v>7.03</v>
@@ -3325,37 +3325,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M25">
-        <v>11.6223462</v>
+        <v>12.1276656</v>
       </c>
       <c r="N25">
-        <v>-8.887346200000001</v>
+        <v>-9.392665600000003</v>
       </c>
       <c r="O25">
-        <v>-1.77746924</v>
+        <v>-1.878533120000001</v>
       </c>
       <c r="P25">
-        <v>-7.109876960000001</v>
+        <v>-7.514132480000002</v>
       </c>
       <c r="Q25">
-        <v>-5.169876960000001</v>
+        <v>-5.574132480000002</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08302887466821286</v>
+        <v>0.08351872828226831</v>
       </c>
       <c r="T25">
-        <v>0.7256600613514489</v>
+        <v>0.7352082200534418</v>
       </c>
       <c r="U25">
         <v>0.2358</v>
       </c>
       <c r="V25">
-        <v>0.04706450750881951</v>
+        <v>0.04510348636261869</v>
       </c>
       <c r="W25">
-        <v>0.2247021891294204</v>
+        <v>0.2251645979156945</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3363,7 +3363,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.2353225375440975</v>
+        <v>0.2255174318130935</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3371,22 +3371,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1175137369942906</v>
+        <v>0.1194137369942906</v>
       </c>
       <c r="C26">
-        <v>39.07062317379885</v>
+        <v>34.77316137759202</v>
       </c>
       <c r="D26">
-        <v>83.47262317379885</v>
+        <v>81.31816137759202</v>
       </c>
       <c r="E26">
-        <v>16.432</v>
+        <v>18.575</v>
       </c>
       <c r="F26">
-        <v>51.432</v>
+        <v>53.575</v>
       </c>
       <c r="G26">
         <v>7.03</v>
@@ -3407,37 +3407,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M26">
-        <v>12.1276656</v>
+        <v>12.632985</v>
       </c>
       <c r="N26">
-        <v>-9.392665600000001</v>
+        <v>-9.897985000000002</v>
       </c>
       <c r="O26">
-        <v>-1.87853312</v>
+        <v>-1.979597</v>
       </c>
       <c r="P26">
-        <v>-7.514132480000001</v>
+        <v>-7.918388000000002</v>
       </c>
       <c r="Q26">
-        <v>-5.57413248</v>
+        <v>-5.978388000000002</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08351872828226831</v>
+        <v>0.08402164465936521</v>
       </c>
       <c r="T26">
-        <v>0.7352082200534418</v>
+        <v>0.7450109963208209</v>
       </c>
       <c r="U26">
         <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.0451034863626187</v>
+        <v>0.04329934690811395</v>
       </c>
       <c r="W26">
-        <v>0.2251645979156945</v>
+        <v>0.2255900139990667</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>0.2255174318130935</v>
+        <v>0.2164967345405697</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3453,22 +3453,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1194137369942906</v>
+        <v>0.1213137369942906</v>
       </c>
       <c r="C27">
-        <v>34.77316137759202</v>
+        <v>30.58411634304279</v>
       </c>
       <c r="D27">
-        <v>81.31816137759202</v>
+        <v>79.2721163430428</v>
       </c>
       <c r="E27">
-        <v>18.575</v>
+        <v>20.718</v>
       </c>
       <c r="F27">
-        <v>53.575</v>
+        <v>55.718</v>
       </c>
       <c r="G27">
         <v>7.03</v>
@@ -3489,37 +3489,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M27">
-        <v>12.632985</v>
+        <v>13.1383044</v>
       </c>
       <c r="N27">
-        <v>-9.897985000000002</v>
+        <v>-10.4033044</v>
       </c>
       <c r="O27">
-        <v>-1.979597</v>
+        <v>-2.08066088</v>
       </c>
       <c r="P27">
-        <v>-7.918388000000002</v>
+        <v>-8.322643520000002</v>
       </c>
       <c r="Q27">
-        <v>-5.978388000000002</v>
+        <v>-6.382643520000001</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08402164465936521</v>
+        <v>0.08453815337097825</v>
       </c>
       <c r="T27">
-        <v>0.7450109963208209</v>
+        <v>0.7550787124873186</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.04329934690811395</v>
+        <v>0.04163398741164803</v>
       </c>
       <c r="W27">
-        <v>0.2255900139990667</v>
+        <v>0.2259827057683334</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.2164967345405697</v>
+        <v>0.2081699370582402</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3535,22 +3535,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1213137369942906</v>
+        <v>0.1232137369942906</v>
       </c>
       <c r="C28">
-        <v>30.58411634304279</v>
+        <v>26.49550530681428</v>
       </c>
       <c r="D28">
-        <v>79.2721163430428</v>
+        <v>77.32650530681428</v>
       </c>
       <c r="E28">
-        <v>20.718</v>
+        <v>22.861</v>
       </c>
       <c r="F28">
-        <v>55.718</v>
+        <v>57.861</v>
       </c>
       <c r="G28">
         <v>7.03</v>
@@ -3571,37 +3571,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M28">
-        <v>13.1383044</v>
+        <v>13.6436238</v>
       </c>
       <c r="N28">
-        <v>-10.4033044</v>
+        <v>-10.9086238</v>
       </c>
       <c r="O28">
-        <v>-2.08066088</v>
+        <v>-2.181724760000001</v>
       </c>
       <c r="P28">
-        <v>-8.322643520000002</v>
+        <v>-8.726899040000003</v>
       </c>
       <c r="Q28">
-        <v>-6.382643520000001</v>
+        <v>-6.786899040000002</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08453815337097825</v>
+        <v>0.08506881300619715</v>
       </c>
       <c r="T28">
-        <v>0.7550787124873186</v>
+        <v>0.7654222564939943</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.04163398741164803</v>
+        <v>0.04009198787788328</v>
       </c>
       <c r="W28">
-        <v>0.2259827057683334</v>
+        <v>0.2263463092583951</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.2081699370582402</v>
+        <v>0.2004599393894164</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3617,22 +3617,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1232137369942906</v>
+        <v>0.1251137369942906</v>
       </c>
       <c r="C29">
-        <v>26.49550530681428</v>
+        <v>22.50011042982691</v>
       </c>
       <c r="D29">
-        <v>77.32650530681428</v>
+        <v>75.47411042982692</v>
       </c>
       <c r="E29">
-        <v>22.861</v>
+        <v>25.00400000000001</v>
       </c>
       <c r="F29">
-        <v>57.861</v>
+        <v>60.00400000000001</v>
       </c>
       <c r="G29">
         <v>7.03</v>
@@ -3653,37 +3653,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M29">
-        <v>13.6436238</v>
+        <v>14.1489432</v>
       </c>
       <c r="N29">
-        <v>-10.9086238</v>
+        <v>-11.4139432</v>
       </c>
       <c r="O29">
-        <v>-2.181724760000001</v>
+        <v>-2.282788640000001</v>
       </c>
       <c r="P29">
-        <v>-8.726899040000003</v>
+        <v>-9.131154560000002</v>
       </c>
       <c r="Q29">
-        <v>-6.786899040000002</v>
+        <v>-7.191154560000002</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08506881300619715</v>
+        <v>0.08561421318683876</v>
       </c>
       <c r="T29">
-        <v>0.7654222564939943</v>
+        <v>0.7760531211675219</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.04009198787788328</v>
+        <v>0.03866013116795888</v>
       </c>
       <c r="W29">
-        <v>0.2263463092583951</v>
+        <v>0.2266839410705953</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.2004599393894164</v>
+        <v>0.1933006558397944</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3699,22 +3699,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1251137369942906</v>
+        <v>0.1270137369942906</v>
       </c>
       <c r="C30">
-        <v>22.50011042982691</v>
+        <v>18.59138932002561</v>
       </c>
       <c r="D30">
-        <v>75.47411042982692</v>
+        <v>73.70838932002562</v>
       </c>
       <c r="E30">
-        <v>25.00400000000001</v>
+        <v>27.14700000000001</v>
       </c>
       <c r="F30">
-        <v>60.00400000000001</v>
+        <v>62.14700000000001</v>
       </c>
       <c r="G30">
         <v>7.03</v>
@@ -3735,37 +3735,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M30">
-        <v>14.1489432</v>
+        <v>14.6542626</v>
       </c>
       <c r="N30">
-        <v>-11.4139432</v>
+        <v>-11.91926260000001</v>
       </c>
       <c r="O30">
-        <v>-2.282788640000001</v>
+        <v>-2.383852520000001</v>
       </c>
       <c r="P30">
-        <v>-9.131154560000002</v>
+        <v>-9.535410080000004</v>
       </c>
       <c r="Q30">
-        <v>-7.191154560000002</v>
+        <v>-7.595410080000003</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.08561421318683876</v>
+        <v>0.08617497675285059</v>
       </c>
       <c r="T30">
-        <v>0.7760531211675219</v>
+        <v>0.7869834468177688</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.03866013116795888</v>
+        <v>0.03732702319664995</v>
       </c>
       <c r="W30">
-        <v>0.2266839410705953</v>
+        <v>0.2269982879302299</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.1933006558397944</v>
+        <v>0.1866351159832497</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3781,22 +3781,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1270137369942906</v>
+        <v>0.1289137369942906</v>
       </c>
       <c r="C31">
-        <v>18.59138932002563</v>
+        <v>14.76339782797335</v>
       </c>
       <c r="D31">
-        <v>73.70838932002563</v>
+        <v>72.02339782797335</v>
       </c>
       <c r="E31">
-        <v>27.147</v>
+        <v>29.29000000000001</v>
       </c>
       <c r="F31">
-        <v>62.147</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G31">
         <v>7.03</v>
@@ -3817,37 +3817,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M31">
-        <v>14.6542626</v>
+        <v>15.159582</v>
       </c>
       <c r="N31">
-        <v>-11.9192626</v>
+        <v>-12.424582</v>
       </c>
       <c r="O31">
-        <v>-2.38385252</v>
+        <v>-2.484916400000001</v>
       </c>
       <c r="P31">
-        <v>-9.535410080000002</v>
+        <v>-9.939665600000001</v>
       </c>
       <c r="Q31">
-        <v>-7.595410080000002</v>
+        <v>-7.999665600000001</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08617497675285057</v>
+        <v>0.08675176213503416</v>
       </c>
       <c r="T31">
-        <v>0.7869834468177687</v>
+        <v>0.7982260674865939</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.03732702319664995</v>
+        <v>0.03608278909009496</v>
       </c>
       <c r="W31">
-        <v>0.2269982879302299</v>
+        <v>0.2272916783325556</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.1866351159832498</v>
+        <v>0.1804139454504747</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3863,22 +3863,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1289137369942906</v>
+        <v>0.1308137369942906</v>
       </c>
       <c r="C32">
-        <v>14.76339782797335</v>
+        <v>11.01072319524498</v>
       </c>
       <c r="D32">
-        <v>72.02339782797335</v>
+        <v>70.41372319524498</v>
       </c>
       <c r="E32">
-        <v>29.29000000000001</v>
+        <v>31.43300000000001</v>
       </c>
       <c r="F32">
-        <v>64.29000000000001</v>
+        <v>66.43300000000001</v>
       </c>
       <c r="G32">
         <v>7.03</v>
@@ -3899,37 +3899,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M32">
-        <v>15.159582</v>
+        <v>15.6649014</v>
       </c>
       <c r="N32">
-        <v>-12.424582</v>
+        <v>-12.9299014</v>
       </c>
       <c r="O32">
-        <v>-2.484916400000001</v>
+        <v>-2.585980280000001</v>
       </c>
       <c r="P32">
-        <v>-9.939665600000001</v>
+        <v>-10.34392112</v>
       </c>
       <c r="Q32">
-        <v>-7.999665600000001</v>
+        <v>-8.403921120000001</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08675176213503416</v>
+        <v>0.08734526593409263</v>
       </c>
       <c r="T32">
-        <v>0.7982260674865939</v>
+        <v>0.8097945612182837</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.03608278909009496</v>
+        <v>0.03491882815170479</v>
       </c>
       <c r="W32">
-        <v>0.2272916783325556</v>
+        <v>0.227566140321828</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3937,7 +3937,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.1804139454504747</v>
+        <v>0.174594140758524</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3945,22 +3945,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1308137369942906</v>
+        <v>0.1327137369942906</v>
       </c>
       <c r="C33">
-        <v>11.01072319524498</v>
+        <v>7.328425971380895</v>
       </c>
       <c r="D33">
-        <v>70.41372319524498</v>
+        <v>68.8744259713809</v>
       </c>
       <c r="E33">
-        <v>31.43300000000001</v>
+        <v>33.57600000000001</v>
       </c>
       <c r="F33">
-        <v>66.43300000000001</v>
+        <v>68.57600000000001</v>
       </c>
       <c r="G33">
         <v>7.03</v>
@@ -3981,37 +3981,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M33">
-        <v>15.6649014</v>
+        <v>16.1702208</v>
       </c>
       <c r="N33">
-        <v>-12.9299014</v>
+        <v>-13.4352208</v>
       </c>
       <c r="O33">
-        <v>-2.585980280000001</v>
+        <v>-2.687044160000001</v>
       </c>
       <c r="P33">
-        <v>-10.34392112</v>
+        <v>-10.74817664</v>
       </c>
       <c r="Q33">
-        <v>-8.403921120000001</v>
+        <v>-8.808176640000003</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08734526593409263</v>
+        <v>0.08795622572724104</v>
       </c>
       <c r="T33">
-        <v>0.8097945612182837</v>
+        <v>0.8217033047656114</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.03491882815170479</v>
+        <v>0.03382761477196402</v>
       </c>
       <c r="W33">
-        <v>0.227566140321828</v>
+        <v>0.2278234484367709</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.174594140758524</v>
+        <v>0.16913807385982</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4027,22 +4027,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1327137369942906</v>
+        <v>0.1346137369942906</v>
       </c>
       <c r="C34">
-        <v>7.328425971380895</v>
+        <v>3.711989386294562</v>
       </c>
       <c r="D34">
-        <v>68.8744259713809</v>
+        <v>67.40098938629457</v>
       </c>
       <c r="E34">
-        <v>33.57600000000001</v>
+        <v>35.71900000000001</v>
       </c>
       <c r="F34">
-        <v>68.57600000000001</v>
+        <v>70.71900000000001</v>
       </c>
       <c r="G34">
         <v>7.03</v>
@@ -4063,37 +4063,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M34">
-        <v>16.1702208</v>
+        <v>16.6755402</v>
       </c>
       <c r="N34">
-        <v>-13.4352208</v>
+        <v>-13.9405402</v>
       </c>
       <c r="O34">
-        <v>-2.687044160000001</v>
+        <v>-2.788108040000001</v>
       </c>
       <c r="P34">
-        <v>-10.74817664</v>
+        <v>-11.15243216</v>
       </c>
       <c r="Q34">
-        <v>-8.808176640000003</v>
+        <v>-9.212432160000004</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08795622572724104</v>
+        <v>0.0885854231261551</v>
       </c>
       <c r="T34">
-        <v>0.8217033047656114</v>
+        <v>0.833967533194949</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.03382761477196402</v>
+        <v>0.03280253553644995</v>
       </c>
       <c r="W34">
-        <v>0.2278234484367709</v>
+        <v>0.2280651621205051</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.16913807385982</v>
+        <v>0.1640126776822498</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1346137369942906</v>
+        <v>0.1365137369942906</v>
       </c>
       <c r="C35">
-        <v>3.711989386294562</v>
+        <v>0.1572750850524045</v>
       </c>
       <c r="D35">
-        <v>67.40098938629457</v>
+        <v>65.98927508505241</v>
       </c>
       <c r="E35">
-        <v>35.71900000000001</v>
+        <v>37.86200000000001</v>
       </c>
       <c r="F35">
-        <v>70.71900000000001</v>
+        <v>72.86200000000001</v>
       </c>
       <c r="G35">
         <v>7.03</v>
@@ -4145,37 +4145,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M35">
-        <v>16.6755402</v>
+        <v>17.1808596</v>
       </c>
       <c r="N35">
-        <v>-13.9405402</v>
+        <v>-14.4458596</v>
       </c>
       <c r="O35">
-        <v>-2.788108040000001</v>
+        <v>-2.889171920000001</v>
       </c>
       <c r="P35">
-        <v>-11.15243216</v>
+        <v>-11.55668768</v>
       </c>
       <c r="Q35">
-        <v>-9.212432160000004</v>
+        <v>-9.616687680000002</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.0885854231261551</v>
+        <v>0.08923368711291502</v>
       </c>
       <c r="T35">
-        <v>0.833967533194949</v>
+        <v>0.8466034049100238</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.03280253553644995</v>
+        <v>0.03183775507949555</v>
       </c>
       <c r="W35">
-        <v>0.2280651621205051</v>
+        <v>0.228292657352255</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4183,7 +4183,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.1640126776822498</v>
+        <v>0.1591887753974778</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4191,22 +4191,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1365137369942906</v>
+        <v>0.1384137369942906</v>
       </c>
       <c r="C36">
-        <v>0.1572750850524045</v>
+        <v>-3.339515688656775</v>
       </c>
       <c r="D36">
-        <v>65.98927508505241</v>
+        <v>64.63548431134323</v>
       </c>
       <c r="E36">
-        <v>37.86200000000001</v>
+        <v>40.00500000000001</v>
       </c>
       <c r="F36">
-        <v>72.86200000000001</v>
+        <v>75.00500000000001</v>
       </c>
       <c r="G36">
         <v>7.03</v>
@@ -4227,37 +4227,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M36">
-        <v>17.1808596</v>
+        <v>17.686179</v>
       </c>
       <c r="N36">
-        <v>-14.4458596</v>
+        <v>-14.951179</v>
       </c>
       <c r="O36">
-        <v>-2.889171920000001</v>
+        <v>-2.990235800000001</v>
       </c>
       <c r="P36">
-        <v>-11.55668768</v>
+        <v>-11.9609432</v>
       </c>
       <c r="Q36">
-        <v>-9.616687680000002</v>
+        <v>-10.0209432</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08923368711291502</v>
+        <v>0.08990189768388293</v>
       </c>
       <c r="T36">
-        <v>0.8466034049100238</v>
+        <v>0.8596280726778703</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.03183775507949555</v>
+        <v>0.0309281049343671</v>
       </c>
       <c r="W36">
-        <v>0.228292657352255</v>
+        <v>0.2285071528564762</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4265,7 +4265,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.1591887753974778</v>
+        <v>0.1546405246718355</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4273,22 +4273,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1384137369942906</v>
+        <v>0.1403137369942906</v>
       </c>
       <c r="C37">
-        <v>-3.339515688656775</v>
+        <v>-6.781876227103936</v>
       </c>
       <c r="D37">
-        <v>64.63548431134323</v>
+        <v>63.33612377289608</v>
       </c>
       <c r="E37">
-        <v>40.00500000000001</v>
+        <v>42.14800000000001</v>
       </c>
       <c r="F37">
-        <v>75.00500000000001</v>
+        <v>77.14800000000001</v>
       </c>
       <c r="G37">
         <v>7.03</v>
@@ -4309,37 +4309,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M37">
-        <v>17.686179</v>
+        <v>18.1914984</v>
       </c>
       <c r="N37">
-        <v>-14.951179</v>
+        <v>-15.4564984</v>
       </c>
       <c r="O37">
-        <v>-2.990235800000001</v>
+        <v>-3.091299680000001</v>
       </c>
       <c r="P37">
-        <v>-11.9609432</v>
+        <v>-12.36519872</v>
       </c>
       <c r="Q37">
-        <v>-10.0209432</v>
+        <v>-10.42519872</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08990189768388293</v>
+        <v>0.09059098983519362</v>
       </c>
       <c r="T37">
-        <v>0.8596280726778703</v>
+        <v>0.8730597613134622</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.0309281049343671</v>
+        <v>0.03006899090841246</v>
       </c>
       <c r="W37">
-        <v>0.2285071528564762</v>
+        <v>0.2287097319437964</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4347,7 +4347,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.1546405246718355</v>
+        <v>0.1503449545420623</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4355,22 +4355,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1403137369942906</v>
+        <v>0.1422137369942906</v>
       </c>
       <c r="C38">
-        <v>-6.781876227103922</v>
+        <v>-10.17302445701465</v>
       </c>
       <c r="D38">
-        <v>63.33612377289608</v>
+        <v>62.08797554298535</v>
       </c>
       <c r="E38">
-        <v>42.148</v>
+        <v>44.291</v>
       </c>
       <c r="F38">
-        <v>77.148</v>
+        <v>79.291</v>
       </c>
       <c r="G38">
         <v>7.03</v>
@@ -4391,37 +4391,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M38">
-        <v>18.1914984</v>
+        <v>18.6968178</v>
       </c>
       <c r="N38">
-        <v>-15.4564984</v>
+        <v>-15.9618178</v>
       </c>
       <c r="O38">
-        <v>-3.091299680000001</v>
+        <v>-3.19236356</v>
       </c>
       <c r="P38">
-        <v>-12.36519872</v>
+        <v>-12.76945424</v>
       </c>
       <c r="Q38">
-        <v>-10.42519872</v>
+        <v>-10.82945424</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.09059098983519362</v>
+        <v>0.09130195792781573</v>
       </c>
       <c r="T38">
-        <v>0.8730597613134621</v>
+        <v>0.8869178527628822</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.03006899090841246</v>
+        <v>0.02925631547845537</v>
       </c>
       <c r="W38">
-        <v>0.2287097319437964</v>
+        <v>0.2289013608101802</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4429,7 +4429,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.1503449545420623</v>
+        <v>0.1462815773922769</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4437,22 +4437,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1422137369942906</v>
+        <v>0.1441137369942906</v>
       </c>
       <c r="C39">
-        <v>-10.17302445701465</v>
+        <v>-13.515929547984</v>
       </c>
       <c r="D39">
-        <v>62.08797554298535</v>
+        <v>60.88807045201601</v>
       </c>
       <c r="E39">
-        <v>44.291</v>
+        <v>46.43400000000001</v>
       </c>
       <c r="F39">
-        <v>79.291</v>
+        <v>81.43400000000001</v>
       </c>
       <c r="G39">
         <v>7.03</v>
@@ -4473,37 +4473,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M39">
-        <v>18.6968178</v>
+        <v>19.2021372</v>
       </c>
       <c r="N39">
-        <v>-15.9618178</v>
+        <v>-16.4671372</v>
       </c>
       <c r="O39">
-        <v>-3.19236356</v>
+        <v>-3.293427440000001</v>
       </c>
       <c r="P39">
-        <v>-12.76945424</v>
+        <v>-13.17370976</v>
       </c>
       <c r="Q39">
-        <v>-10.82945424</v>
+        <v>-11.23370976</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.09130195792781573</v>
+        <v>0.09203586047503856</v>
       </c>
       <c r="T39">
-        <v>0.8869178527628822</v>
+        <v>0.9012229794203479</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.02925631547845537</v>
+        <v>0.02848641243954865</v>
       </c>
       <c r="W39">
-        <v>0.2289013608101802</v>
+        <v>0.2290829039467544</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.1462815773922769</v>
+        <v>0.1424320621977432</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4519,22 +4519,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1441137369942906</v>
+        <v>0.1460137369942906</v>
       </c>
       <c r="C40">
-        <v>-13.515929547984</v>
+        <v>-16.81333549400139</v>
       </c>
       <c r="D40">
-        <v>60.88807045201601</v>
+        <v>59.73366450599863</v>
       </c>
       <c r="E40">
-        <v>46.43400000000001</v>
+        <v>48.57700000000001</v>
       </c>
       <c r="F40">
-        <v>81.43400000000001</v>
+        <v>83.57700000000001</v>
       </c>
       <c r="G40">
         <v>7.03</v>
@@ -4555,37 +4555,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M40">
-        <v>19.2021372</v>
+        <v>19.7074566</v>
       </c>
       <c r="N40">
-        <v>-16.4671372</v>
+        <v>-16.9724566</v>
       </c>
       <c r="O40">
-        <v>-3.293427440000001</v>
+        <v>-3.394491320000001</v>
       </c>
       <c r="P40">
-        <v>-13.17370976</v>
+        <v>-13.57796528</v>
       </c>
       <c r="Q40">
-        <v>-11.23370976</v>
+        <v>-11.63796528</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09203586047503856</v>
+        <v>0.09279382540085887</v>
       </c>
       <c r="T40">
-        <v>0.9012229794203479</v>
+        <v>0.9159971266239603</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.02848641243954865</v>
+        <v>0.02775599160776535</v>
       </c>
       <c r="W40">
-        <v>0.2290829039467544</v>
+        <v>0.229255137178889</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.1424320621977432</v>
+        <v>0.1387799580388267</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4601,22 +4601,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1460137369942906</v>
+        <v>0.1479137369942906</v>
       </c>
       <c r="C41">
-        <v>-16.81333549400139</v>
+        <v>-20.06778206232886</v>
       </c>
       <c r="D41">
-        <v>59.73366450599863</v>
+        <v>58.62221793767116</v>
       </c>
       <c r="E41">
-        <v>48.57700000000001</v>
+        <v>50.72000000000001</v>
       </c>
       <c r="F41">
-        <v>83.57700000000001</v>
+        <v>85.72000000000001</v>
       </c>
       <c r="G41">
         <v>7.03</v>
@@ -4637,37 +4637,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M41">
-        <v>19.7074566</v>
+        <v>20.21277600000001</v>
       </c>
       <c r="N41">
-        <v>-16.9724566</v>
+        <v>-17.47777600000001</v>
       </c>
       <c r="O41">
-        <v>-3.394491320000001</v>
+        <v>-3.495555200000001</v>
       </c>
       <c r="P41">
-        <v>-13.57796528</v>
+        <v>-13.9822208</v>
       </c>
       <c r="Q41">
-        <v>-11.63796528</v>
+        <v>-12.0422208</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09279382540085887</v>
+        <v>0.09357705582420653</v>
       </c>
       <c r="T41">
-        <v>0.9159971266239603</v>
+        <v>0.9312637454010263</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.02775599160776535</v>
+        <v>0.02706209181757121</v>
       </c>
       <c r="W41">
-        <v>0.229255137178889</v>
+        <v>0.2294187587494167</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.1387799580388267</v>
+        <v>0.1353104590878561</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4683,22 +4683,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1479137369942906</v>
+        <v>0.1498137369942906</v>
       </c>
       <c r="C42">
-        <v>-20.06778206232886</v>
+        <v>-23.28162344636344</v>
       </c>
       <c r="D42">
-        <v>58.62221793767116</v>
+        <v>57.55137655363657</v>
       </c>
       <c r="E42">
-        <v>50.72000000000001</v>
+        <v>52.86300000000001</v>
       </c>
       <c r="F42">
-        <v>85.72000000000001</v>
+        <v>87.86300000000001</v>
       </c>
       <c r="G42">
         <v>7.03</v>
@@ -4719,37 +4719,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M42">
-        <v>20.21277600000001</v>
+        <v>20.7180954</v>
       </c>
       <c r="N42">
-        <v>-17.47777600000001</v>
+        <v>-17.9830954</v>
       </c>
       <c r="O42">
-        <v>-3.495555200000001</v>
+        <v>-3.596619080000001</v>
       </c>
       <c r="P42">
-        <v>-13.9822208</v>
+        <v>-14.38647632</v>
       </c>
       <c r="Q42">
-        <v>-12.0422208</v>
+        <v>-12.44647632</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09357705582420653</v>
+        <v>0.09438683643139646</v>
       </c>
       <c r="T42">
-        <v>0.9312637454010263</v>
+        <v>0.9470478766790098</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.02706209181757121</v>
+        <v>0.02640204079763046</v>
       </c>
       <c r="W42">
-        <v>0.2294187587494167</v>
+        <v>0.2295743987799188</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.1353104590878561</v>
+        <v>0.1320102039881522</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4765,22 +4765,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1498137369942906</v>
+        <v>0.1517137369942906</v>
       </c>
       <c r="C43">
-        <v>-23.28162344636344</v>
+        <v>-26.45704491080297</v>
       </c>
       <c r="D43">
-        <v>57.55137655363657</v>
+        <v>56.51895508919704</v>
       </c>
       <c r="E43">
-        <v>52.86300000000001</v>
+        <v>55.00600000000001</v>
       </c>
       <c r="F43">
-        <v>87.86300000000001</v>
+        <v>90.00600000000001</v>
       </c>
       <c r="G43">
         <v>7.03</v>
@@ -4801,37 +4801,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M43">
-        <v>20.7180954</v>
+        <v>21.2234148</v>
       </c>
       <c r="N43">
-        <v>-17.9830954</v>
+        <v>-18.4884148</v>
       </c>
       <c r="O43">
-        <v>-3.596619080000001</v>
+        <v>-3.697682960000001</v>
       </c>
       <c r="P43">
-        <v>-14.38647632</v>
+        <v>-14.79073184</v>
       </c>
       <c r="Q43">
-        <v>-12.44647632</v>
+        <v>-12.85073184</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09438683643139646</v>
+        <v>0.09522454050779985</v>
       </c>
       <c r="T43">
-        <v>0.9470478766790098</v>
+        <v>0.9633762883458893</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.02640204079763046</v>
+        <v>0.02577342077863925</v>
       </c>
       <c r="W43">
-        <v>0.2295743987799188</v>
+        <v>0.2297226273803969</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.1320102039881522</v>
+        <v>0.1288671038931962</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4847,22 +4847,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1517137369942906</v>
+        <v>0.1536137369942906</v>
       </c>
       <c r="C44">
-        <v>-26.45704491080294</v>
+        <v>-29.59607767678677</v>
       </c>
       <c r="D44">
-        <v>56.51895508919706</v>
+        <v>55.52292232321323</v>
       </c>
       <c r="E44">
-        <v>55.006</v>
+        <v>57.149</v>
       </c>
       <c r="F44">
-        <v>90.006</v>
+        <v>92.149</v>
       </c>
       <c r="G44">
         <v>7.03</v>
@@ -4883,37 +4883,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M44">
-        <v>21.2234148</v>
+        <v>21.7287342</v>
       </c>
       <c r="N44">
-        <v>-18.4884148</v>
+        <v>-18.9937342</v>
       </c>
       <c r="O44">
-        <v>-3.69768296</v>
+        <v>-3.798746840000001</v>
       </c>
       <c r="P44">
-        <v>-14.79073184</v>
+        <v>-15.19498736</v>
       </c>
       <c r="Q44">
-        <v>-12.85073184</v>
+        <v>-13.25498736</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09522454050779984</v>
+        <v>0.09609163770969108</v>
       </c>
       <c r="T44">
-        <v>0.9633762883458891</v>
+        <v>0.9802776267379224</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.02577342077863926</v>
+        <v>0.02517403890006625</v>
       </c>
       <c r="W44">
-        <v>0.2297226273803969</v>
+        <v>0.2298639616273644</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4921,7 +4921,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.1288671038931962</v>
+        <v>0.1258701945003312</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4929,22 +4929,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1536137369942906</v>
+        <v>0.1555137369942906</v>
       </c>
       <c r="C45">
-        <v>-29.59607767678677</v>
+        <v>-32.70061226036946</v>
       </c>
       <c r="D45">
-        <v>55.52292232321323</v>
+        <v>54.56138773963054</v>
       </c>
       <c r="E45">
-        <v>57.149</v>
+        <v>59.292</v>
       </c>
       <c r="F45">
-        <v>92.149</v>
+        <v>94.292</v>
       </c>
       <c r="G45">
         <v>7.03</v>
@@ -4965,37 +4965,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M45">
-        <v>21.7287342</v>
+        <v>22.2340536</v>
       </c>
       <c r="N45">
-        <v>-18.9937342</v>
+        <v>-19.4990536</v>
       </c>
       <c r="O45">
-        <v>-3.798746840000001</v>
+        <v>-3.899810720000001</v>
       </c>
       <c r="P45">
-        <v>-15.19498736</v>
+        <v>-15.59924288</v>
       </c>
       <c r="Q45">
-        <v>-13.25498736</v>
+        <v>-13.65924288</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09609163770969108</v>
+        <v>0.0969897026687927</v>
       </c>
       <c r="T45">
-        <v>0.9802776267379224</v>
+        <v>0.9977825843582424</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.02517403890006625</v>
+        <v>0.02460190165233747</v>
       </c>
       <c r="W45">
-        <v>0.2298639616273644</v>
+        <v>0.2299988715903789</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.1258701945003312</v>
+        <v>0.1230095082616873</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5011,22 +5011,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1555137369942906</v>
+        <v>0.1574137369942906</v>
       </c>
       <c r="C46">
-        <v>-32.70061226036946</v>
+        <v>-35.77241044863011</v>
       </c>
       <c r="D46">
-        <v>54.56138773963054</v>
+        <v>53.63258955136989</v>
       </c>
       <c r="E46">
-        <v>59.292</v>
+        <v>61.435</v>
       </c>
       <c r="F46">
-        <v>94.292</v>
+        <v>96.435</v>
       </c>
       <c r="G46">
         <v>7.03</v>
@@ -5047,37 +5047,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M46">
-        <v>22.2340536</v>
+        <v>22.739373</v>
       </c>
       <c r="N46">
-        <v>-19.4990536</v>
+        <v>-20.004373</v>
       </c>
       <c r="O46">
-        <v>-3.899810720000001</v>
+        <v>-4.0008746</v>
       </c>
       <c r="P46">
-        <v>-15.59924288</v>
+        <v>-16.0034984</v>
       </c>
       <c r="Q46">
-        <v>-13.65924288</v>
+        <v>-14.0634984</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.0969897026687927</v>
+        <v>0.09792042453549801</v>
       </c>
       <c r="T46">
-        <v>0.9977825843582424</v>
+        <v>1.015924085892029</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.02460190165233747</v>
+        <v>0.02405519272672997</v>
       </c>
       <c r="W46">
-        <v>0.2299988715903789</v>
+        <v>0.2301277855550371</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.1230095082616873</v>
+        <v>0.1202759636336499</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5093,22 +5093,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1574137369942906</v>
+        <v>0.1593137369942906</v>
       </c>
       <c r="C47">
-        <v>-35.77241044863011</v>
+        <v>-38.81311607304038</v>
       </c>
       <c r="D47">
-        <v>53.63258955136989</v>
+        <v>52.73488392695962</v>
       </c>
       <c r="E47">
-        <v>61.435</v>
+        <v>63.578</v>
       </c>
       <c r="F47">
-        <v>96.435</v>
+        <v>98.578</v>
       </c>
       <c r="G47">
         <v>7.03</v>
@@ -5129,37 +5129,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M47">
-        <v>22.739373</v>
+        <v>23.2446924</v>
       </c>
       <c r="N47">
-        <v>-20.004373</v>
+        <v>-20.5096924</v>
       </c>
       <c r="O47">
-        <v>-4.0008746</v>
+        <v>-4.10193848</v>
       </c>
       <c r="P47">
-        <v>-16.0034984</v>
+        <v>-16.40775392</v>
       </c>
       <c r="Q47">
-        <v>-14.0634984</v>
+        <v>-14.46775392</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09792042453549801</v>
+        <v>0.09888561758245168</v>
       </c>
       <c r="T47">
-        <v>1.015924085892029</v>
+        <v>1.034737494890029</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.02405519272672997</v>
+        <v>0.02353225375440975</v>
       </c>
       <c r="W47">
-        <v>0.2301277855550371</v>
+        <v>0.2302510945647102</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5167,7 +5167,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.1202759636336499</v>
+        <v>0.1176612687720487</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1593137369942906</v>
+        <v>0.1612137369942906</v>
       </c>
       <c r="C48">
-        <v>-38.81311607304038</v>
+        <v>-41.82426471869233</v>
       </c>
       <c r="D48">
-        <v>52.73488392695962</v>
+        <v>51.86673528130769</v>
       </c>
       <c r="E48">
-        <v>63.578</v>
+        <v>65.72100000000002</v>
       </c>
       <c r="F48">
-        <v>98.578</v>
+        <v>100.721</v>
       </c>
       <c r="G48">
         <v>7.03</v>
@@ -5211,37 +5211,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M48">
-        <v>23.2446924</v>
+        <v>23.75001180000001</v>
       </c>
       <c r="N48">
-        <v>-20.5096924</v>
+        <v>-21.01501180000001</v>
       </c>
       <c r="O48">
-        <v>-4.10193848</v>
+        <v>-4.203002360000002</v>
       </c>
       <c r="P48">
-        <v>-16.40775392</v>
+        <v>-16.81200944</v>
       </c>
       <c r="Q48">
-        <v>-14.46775392</v>
+        <v>-14.87200944</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09888561758245168</v>
+        <v>0.09988723300853568</v>
       </c>
       <c r="T48">
-        <v>1.034737494890029</v>
+        <v>1.054260843850218</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.02353225375440975</v>
+        <v>0.02303156750431593</v>
       </c>
       <c r="W48">
-        <v>0.2302510945647102</v>
+        <v>0.2303691563824823</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.1176612687720487</v>
+        <v>0.1151578375215796</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5257,22 +5257,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1612137369942906</v>
+        <v>0.1631137369942906</v>
       </c>
       <c r="C49">
-        <v>-41.82426471869233</v>
+        <v>-44.80729249002895</v>
       </c>
       <c r="D49">
-        <v>51.86673528130769</v>
+        <v>51.02670750997107</v>
       </c>
       <c r="E49">
-        <v>65.72100000000002</v>
+        <v>67.86400000000002</v>
       </c>
       <c r="F49">
-        <v>100.721</v>
+        <v>102.864</v>
       </c>
       <c r="G49">
         <v>7.03</v>
@@ -5293,37 +5293,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M49">
-        <v>23.75001180000001</v>
+        <v>24.2553312</v>
       </c>
       <c r="N49">
-        <v>-21.01501180000001</v>
+        <v>-21.5203312</v>
       </c>
       <c r="O49">
-        <v>-4.203002360000002</v>
+        <v>-4.304066240000001</v>
       </c>
       <c r="P49">
-        <v>-16.81200944</v>
+        <v>-17.21626496</v>
       </c>
       <c r="Q49">
-        <v>-14.87200944</v>
+        <v>-15.27626496</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09988723300853568</v>
+        <v>0.1009273721048537</v>
       </c>
       <c r="T49">
-        <v>1.054260843850218</v>
+        <v>1.074535090847338</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.02303156750431593</v>
+        <v>0.02255174318130935</v>
       </c>
       <c r="W49">
-        <v>0.2303691563824823</v>
+        <v>0.2304822989578472</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.1151578375215796</v>
+        <v>0.1127587159065467</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5339,22 +5339,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1631137369942906</v>
+        <v>0.1650137369942906</v>
       </c>
       <c r="C50">
-        <v>-44.80729249002894</v>
+        <v>-47.76354393833802</v>
       </c>
       <c r="D50">
-        <v>51.02670750997107</v>
+        <v>50.21345606166198</v>
       </c>
       <c r="E50">
-        <v>67.864</v>
+        <v>70.00700000000001</v>
       </c>
       <c r="F50">
-        <v>102.864</v>
+        <v>105.007</v>
       </c>
       <c r="G50">
         <v>7.03</v>
@@ -5375,37 +5375,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M50">
-        <v>24.2553312</v>
+        <v>24.7606506</v>
       </c>
       <c r="N50">
-        <v>-21.5203312</v>
+        <v>-22.0256506</v>
       </c>
       <c r="O50">
-        <v>-4.30406624</v>
+        <v>-4.405130120000001</v>
       </c>
       <c r="P50">
-        <v>-17.21626496</v>
+        <v>-17.62052048</v>
       </c>
       <c r="Q50">
-        <v>-15.27626496</v>
+        <v>-15.68052048</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1009273721048537</v>
+        <v>0.1020083009696547</v>
       </c>
       <c r="T50">
-        <v>1.074535090847338</v>
+        <v>1.095604406354148</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.02255174318130935</v>
+        <v>0.02209150352454793</v>
       </c>
       <c r="W50">
-        <v>0.2304822989578472</v>
+        <v>0.2305908234689116</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.1127587159065467</v>
+        <v>0.1104575176227397</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5421,22 +5421,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1650137369942906</v>
+        <v>0.1669137369942906</v>
       </c>
       <c r="C51">
-        <v>-47.76354393833802</v>
+        <v>-50.69427924305954</v>
       </c>
       <c r="D51">
-        <v>50.21345606166198</v>
+        <v>49.42572075694046</v>
       </c>
       <c r="E51">
-        <v>70.00700000000001</v>
+        <v>72.15000000000001</v>
       </c>
       <c r="F51">
-        <v>105.007</v>
+        <v>107.15</v>
       </c>
       <c r="G51">
         <v>7.03</v>
@@ -5457,37 +5457,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M51">
-        <v>24.7606506</v>
+        <v>25.26597</v>
       </c>
       <c r="N51">
-        <v>-22.0256506</v>
+        <v>-22.53097</v>
       </c>
       <c r="O51">
-        <v>-4.405130120000001</v>
+        <v>-4.506194000000001</v>
       </c>
       <c r="P51">
-        <v>-17.62052048</v>
+        <v>-18.024776</v>
       </c>
       <c r="Q51">
-        <v>-15.68052048</v>
+        <v>-16.084776</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1020083009696547</v>
+        <v>0.1031324669890478</v>
       </c>
       <c r="T51">
-        <v>1.095604406354148</v>
+        <v>1.117516494481231</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.02209150352454793</v>
+        <v>0.02164967345405697</v>
       </c>
       <c r="W51">
-        <v>0.2305908234689116</v>
+        <v>0.2306950069995334</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5495,7 +5495,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.1104575176227397</v>
+        <v>0.1082483672702849</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5503,22 +5503,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1669137369942906</v>
+        <v>0.1688137369942906</v>
       </c>
       <c r="C52">
-        <v>-50.69427924305954</v>
+        <v>-53.60068072758273</v>
       </c>
       <c r="D52">
-        <v>49.42572075694046</v>
+        <v>48.66231927241728</v>
       </c>
       <c r="E52">
-        <v>72.15000000000001</v>
+        <v>74.29300000000001</v>
       </c>
       <c r="F52">
-        <v>107.15</v>
+        <v>109.293</v>
       </c>
       <c r="G52">
         <v>7.03</v>
@@ -5539,37 +5539,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M52">
-        <v>25.26597</v>
+        <v>25.7712894</v>
       </c>
       <c r="N52">
-        <v>-22.53097</v>
+        <v>-23.0362894</v>
       </c>
       <c r="O52">
-        <v>-4.506194000000001</v>
+        <v>-4.607257880000001</v>
       </c>
       <c r="P52">
-        <v>-18.024776</v>
+        <v>-18.42903152</v>
       </c>
       <c r="Q52">
-        <v>-16.084776</v>
+        <v>-16.48903152</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1031324669890478</v>
+        <v>0.1043025173357631</v>
       </c>
       <c r="T52">
-        <v>1.117516494481231</v>
+        <v>1.140322953552277</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.02164967345405697</v>
+        <v>0.02122517005299703</v>
       </c>
       <c r="W52">
-        <v>0.2306950069995334</v>
+        <v>0.2307951049015033</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.1082483672702849</v>
+        <v>0.1061258502649851</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5585,22 +5585,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1688137369942906</v>
+        <v>0.1707137369942906</v>
       </c>
       <c r="C53">
-        <v>-53.60068072758273</v>
+        <v>-56.48385878039223</v>
       </c>
       <c r="D53">
-        <v>48.66231927241728</v>
+        <v>47.92214121960778</v>
       </c>
       <c r="E53">
-        <v>74.29300000000001</v>
+        <v>76.43600000000001</v>
       </c>
       <c r="F53">
-        <v>109.293</v>
+        <v>111.436</v>
       </c>
       <c r="G53">
         <v>7.03</v>
@@ -5621,37 +5621,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M53">
-        <v>25.7712894</v>
+        <v>26.2766088</v>
       </c>
       <c r="N53">
-        <v>-23.0362894</v>
+        <v>-23.5416088</v>
       </c>
       <c r="O53">
-        <v>-4.607257880000001</v>
+        <v>-4.70832176</v>
       </c>
       <c r="P53">
-        <v>-18.42903152</v>
+        <v>-18.83328704</v>
       </c>
       <c r="Q53">
-        <v>-16.48903152</v>
+        <v>-16.89328704</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1043025173357631</v>
+        <v>0.1055213197802582</v>
       </c>
       <c r="T53">
-        <v>1.140322953552277</v>
+        <v>1.164079681751283</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.02122517005299703</v>
+        <v>0.02081699370582402</v>
       </c>
       <c r="W53">
-        <v>0.2307951049015033</v>
+        <v>0.2308913528841667</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.1061258502649851</v>
+        <v>0.1040849685291201</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5667,22 +5667,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1707137369942906</v>
+        <v>0.1726137369942906</v>
       </c>
       <c r="C54">
-        <v>-56.48385878039223</v>
+        <v>-59.34485724392898</v>
       </c>
       <c r="D54">
-        <v>47.92214121960778</v>
+        <v>47.20414275607102</v>
       </c>
       <c r="E54">
-        <v>76.43600000000001</v>
+        <v>78.57900000000001</v>
       </c>
       <c r="F54">
-        <v>111.436</v>
+        <v>113.579</v>
       </c>
       <c r="G54">
         <v>7.03</v>
@@ -5703,37 +5703,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M54">
-        <v>26.2766088</v>
+        <v>26.7819282</v>
       </c>
       <c r="N54">
-        <v>-23.5416088</v>
+        <v>-24.0469282</v>
       </c>
       <c r="O54">
-        <v>-4.70832176</v>
+        <v>-4.809385640000001</v>
       </c>
       <c r="P54">
-        <v>-18.83328704</v>
+        <v>-19.23754256</v>
       </c>
       <c r="Q54">
-        <v>-16.89328704</v>
+        <v>-17.29754256</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1055213197802582</v>
+        <v>0.1067919861585615</v>
       </c>
       <c r="T54">
-        <v>1.164079681751283</v>
+        <v>1.188847334554501</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.02081699370582402</v>
+        <v>0.02042422023967639</v>
       </c>
       <c r="W54">
-        <v>0.2308913528841667</v>
+        <v>0.2309839688674843</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1040849685291201</v>
+        <v>0.1021211011983819</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5749,22 +5749,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1726137369942906</v>
+        <v>0.1745137369942906</v>
       </c>
       <c r="C55">
-        <v>-59.34485724392898</v>
+        <v>-62.18465832616711</v>
       </c>
       <c r="D55">
-        <v>47.20414275607102</v>
+        <v>46.5073416738329</v>
       </c>
       <c r="E55">
-        <v>78.57900000000001</v>
+        <v>80.72200000000001</v>
       </c>
       <c r="F55">
-        <v>113.579</v>
+        <v>115.722</v>
       </c>
       <c r="G55">
         <v>7.03</v>
@@ -5785,37 +5785,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M55">
-        <v>26.7819282</v>
+        <v>27.2872476</v>
       </c>
       <c r="N55">
-        <v>-24.0469282</v>
+        <v>-24.5522476</v>
       </c>
       <c r="O55">
-        <v>-4.809385640000001</v>
+        <v>-4.910449520000001</v>
       </c>
       <c r="P55">
-        <v>-19.23754256</v>
+        <v>-19.64179808</v>
       </c>
       <c r="Q55">
-        <v>-17.29754256</v>
+        <v>-17.70179808</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1067919861585615</v>
+        <v>0.1081178989011389</v>
       </c>
       <c r="T55">
-        <v>1.188847334554501</v>
+        <v>1.214691841827426</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.02042422023967639</v>
+        <v>0.02004599393894164</v>
       </c>
       <c r="W55">
-        <v>0.2309839688674843</v>
+        <v>0.2310731546291976</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5823,7 +5823,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1021211011983819</v>
+        <v>0.1002299696947082</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5831,22 +5831,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1745137369942906</v>
+        <v>0.1764137369942906</v>
       </c>
       <c r="C56">
-        <v>-62.18465832616711</v>
+        <v>-65.00418708350713</v>
       </c>
       <c r="D56">
-        <v>46.5073416738329</v>
+        <v>45.83081291649287</v>
       </c>
       <c r="E56">
-        <v>80.72200000000001</v>
+        <v>82.86500000000001</v>
       </c>
       <c r="F56">
-        <v>115.722</v>
+        <v>117.865</v>
       </c>
       <c r="G56">
         <v>7.03</v>
@@ -5867,37 +5867,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M56">
-        <v>27.2872476</v>
+        <v>27.792567</v>
       </c>
       <c r="N56">
-        <v>-24.5522476</v>
+        <v>-25.057567</v>
       </c>
       <c r="O56">
-        <v>-4.910449520000001</v>
+        <v>-5.011513400000001</v>
       </c>
       <c r="P56">
-        <v>-19.64179808</v>
+        <v>-20.0460536</v>
       </c>
       <c r="Q56">
-        <v>-17.70179808</v>
+        <v>-18.1060536</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1081178989011389</v>
+        <v>0.109502741098942</v>
       </c>
       <c r="T56">
-        <v>1.214691841827426</v>
+        <v>1.241684993868035</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.02004599393894164</v>
+        <v>0.01968152132186998</v>
       </c>
       <c r="W56">
-        <v>0.2310731546291976</v>
+        <v>0.2311590972723031</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5905,7 +5905,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1002299696947082</v>
+        <v>0.09840760660934988</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5913,22 +5913,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1764137369942906</v>
+        <v>0.1783137369942906</v>
       </c>
       <c r="C57">
-        <v>-65.00418708350713</v>
+        <v>-67.80431551801118</v>
       </c>
       <c r="D57">
-        <v>45.83081291649287</v>
+        <v>45.17368448198884</v>
       </c>
       <c r="E57">
-        <v>82.86500000000001</v>
+        <v>85.00800000000002</v>
       </c>
       <c r="F57">
-        <v>117.865</v>
+        <v>120.008</v>
       </c>
       <c r="G57">
         <v>7.03</v>
@@ -5949,37 +5949,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M57">
-        <v>27.792567</v>
+        <v>28.29788640000001</v>
       </c>
       <c r="N57">
-        <v>-25.057567</v>
+        <v>-25.56288640000001</v>
       </c>
       <c r="O57">
-        <v>-5.011513400000001</v>
+        <v>-5.112577280000002</v>
       </c>
       <c r="P57">
-        <v>-20.0460536</v>
+        <v>-20.45030912000001</v>
       </c>
       <c r="Q57">
-        <v>-18.1060536</v>
+        <v>-18.51030912000001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.109502741098942</v>
+        <v>0.1109505306693725</v>
       </c>
       <c r="T57">
-        <v>1.241684993868035</v>
+        <v>1.269905107365036</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.01968152132186998</v>
+        <v>0.01933006558397944</v>
       </c>
       <c r="W57">
-        <v>0.2311590972723031</v>
+        <v>0.2312419705352977</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.09840760660934988</v>
+        <v>0.09665032791989714</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -5995,22 +5995,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1783137369942906</v>
+        <v>0.1802137369942906</v>
       </c>
       <c r="C58">
-        <v>-67.80431551801118</v>
+        <v>-70.58586632714034</v>
       </c>
       <c r="D58">
-        <v>45.17368448198884</v>
+        <v>44.53513367285968</v>
       </c>
       <c r="E58">
-        <v>85.00800000000002</v>
+        <v>87.15100000000002</v>
       </c>
       <c r="F58">
-        <v>120.008</v>
+        <v>122.151</v>
       </c>
       <c r="G58">
         <v>7.03</v>
@@ -6031,37 +6031,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M58">
-        <v>28.29788640000001</v>
+        <v>28.80320580000001</v>
       </c>
       <c r="N58">
-        <v>-25.56288640000001</v>
+        <v>-26.06820580000001</v>
       </c>
       <c r="O58">
-        <v>-5.112577280000002</v>
+        <v>-5.213641160000002</v>
       </c>
       <c r="P58">
-        <v>-20.45030912000001</v>
+        <v>-20.85456464000001</v>
       </c>
       <c r="Q58">
-        <v>-18.51030912000001</v>
+        <v>-18.91456464000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1109505306693725</v>
+        <v>0.1124656592895905</v>
       </c>
       <c r="T58">
-        <v>1.269905107365036</v>
+        <v>1.299437784280502</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.01933006558397944</v>
+        <v>0.01899094162636576</v>
       </c>
       <c r="W58">
-        <v>0.2312419705352977</v>
+        <v>0.231321935964503</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6069,7 +6069,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.09665032791989714</v>
+        <v>0.09495470813182882</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6077,22 +6077,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1802137369942906</v>
+        <v>0.1821137369942906</v>
       </c>
       <c r="C59">
-        <v>-70.58586632714034</v>
+        <v>-73.34961633989931</v>
       </c>
       <c r="D59">
-        <v>44.53513367285968</v>
+        <v>43.9143836601007</v>
       </c>
       <c r="E59">
-        <v>87.15100000000002</v>
+        <v>89.29400000000003</v>
       </c>
       <c r="F59">
-        <v>122.151</v>
+        <v>124.294</v>
       </c>
       <c r="G59">
         <v>7.03</v>
@@ -6113,37 +6113,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M59">
-        <v>28.80320580000001</v>
+        <v>29.30852520000001</v>
       </c>
       <c r="N59">
-        <v>-26.06820580000001</v>
+        <v>-26.57352520000001</v>
       </c>
       <c r="O59">
-        <v>-5.213641160000002</v>
+        <v>-5.314705040000002</v>
       </c>
       <c r="P59">
-        <v>-20.85456464000001</v>
+        <v>-21.25882016000001</v>
       </c>
       <c r="Q59">
-        <v>-18.91456464000001</v>
+        <v>-19.31882016</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1124656592895905</v>
+        <v>0.1140529368917236</v>
       </c>
       <c r="T59">
-        <v>1.299437784280502</v>
+        <v>1.330376779144323</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.01899094162636576</v>
+        <v>0.01866351159832497</v>
       </c>
       <c r="W59">
-        <v>0.231321935964503</v>
+        <v>0.231399143965115</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.09495470813182882</v>
+        <v>0.09331755799162489</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6159,22 +6159,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1821137369942906</v>
+        <v>0.1840137369942906</v>
       </c>
       <c r="C60">
-        <v>-73.34961633989928</v>
+        <v>-76.09629966956457</v>
       </c>
       <c r="D60">
-        <v>43.9143836601007</v>
+        <v>43.31070033043542</v>
       </c>
       <c r="E60">
-        <v>89.294</v>
+        <v>91.437</v>
       </c>
       <c r="F60">
-        <v>124.294</v>
+        <v>126.437</v>
       </c>
       <c r="G60">
         <v>7.03</v>
@@ -6195,37 +6195,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M60">
-        <v>29.3085252</v>
+        <v>29.8138446</v>
       </c>
       <c r="N60">
-        <v>-26.5735252</v>
+        <v>-27.0788446</v>
       </c>
       <c r="O60">
-        <v>-5.314705040000001</v>
+        <v>-5.415768920000001</v>
       </c>
       <c r="P60">
-        <v>-21.25882016</v>
+        <v>-21.66307568</v>
       </c>
       <c r="Q60">
-        <v>-19.31882016</v>
+        <v>-19.72307568</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1140529368917236</v>
+        <v>0.1157176426695705</v>
       </c>
       <c r="T60">
-        <v>1.330376779144323</v>
+        <v>1.362824993269794</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.01866351159832498</v>
+        <v>0.01834718089326862</v>
       </c>
       <c r="W60">
-        <v>0.231399143965115</v>
+        <v>0.2314737347453673</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.09331755799162489</v>
+        <v>0.09173590446634317</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1840137369942906</v>
+        <v>0.1859137369942906</v>
       </c>
       <c r="C61">
-        <v>-76.09629966956457</v>
+        <v>-78.82661060989857</v>
       </c>
       <c r="D61">
-        <v>43.31070033043542</v>
+        <v>42.72338939010145</v>
       </c>
       <c r="E61">
-        <v>91.437</v>
+        <v>93.58000000000001</v>
       </c>
       <c r="F61">
-        <v>126.437</v>
+        <v>128.58</v>
       </c>
       <c r="G61">
         <v>7.03</v>
@@ -6277,37 +6277,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M61">
-        <v>29.8138446</v>
+        <v>30.319164</v>
       </c>
       <c r="N61">
-        <v>-27.0788446</v>
+        <v>-27.584164</v>
       </c>
       <c r="O61">
-        <v>-5.415768920000001</v>
+        <v>-5.516832800000001</v>
       </c>
       <c r="P61">
-        <v>-21.66307568</v>
+        <v>-22.06733120000001</v>
       </c>
       <c r="Q61">
-        <v>-19.72307568</v>
+        <v>-20.1273312</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1157176426695705</v>
+        <v>0.1174655837363098</v>
       </c>
       <c r="T61">
-        <v>1.362824993269794</v>
+        <v>1.396895618101539</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.01834718089326862</v>
+        <v>0.01804139454504748</v>
       </c>
       <c r="W61">
-        <v>0.2314737347453673</v>
+        <v>0.2315458391662778</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6315,7 +6315,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.09173590446634317</v>
+        <v>0.09020697272523737</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6323,22 +6323,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1859137369942906</v>
+        <v>0.1878137369942906</v>
       </c>
       <c r="C62">
-        <v>-78.82661060989857</v>
+        <v>-81.54120629887376</v>
       </c>
       <c r="D62">
-        <v>42.72338939010145</v>
+        <v>42.15179370112625</v>
       </c>
       <c r="E62">
-        <v>93.58000000000001</v>
+        <v>95.72300000000001</v>
       </c>
       <c r="F62">
-        <v>128.58</v>
+        <v>130.723</v>
       </c>
       <c r="G62">
         <v>7.03</v>
@@ -6359,37 +6359,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M62">
-        <v>30.319164</v>
+        <v>30.82448340000001</v>
       </c>
       <c r="N62">
-        <v>-27.584164</v>
+        <v>-28.08948340000001</v>
       </c>
       <c r="O62">
-        <v>-5.516832800000001</v>
+        <v>-5.617896680000001</v>
       </c>
       <c r="P62">
-        <v>-22.06733120000001</v>
+        <v>-22.47158672</v>
       </c>
       <c r="Q62">
-        <v>-20.1273312</v>
+        <v>-20.53158672</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1174655837363098</v>
+        <v>0.1193031628064716</v>
       </c>
       <c r="T62">
-        <v>1.396895618101539</v>
+        <v>1.432713454463117</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.01804139454504748</v>
+        <v>0.01774563397873522</v>
       </c>
       <c r="W62">
-        <v>0.2315458391662778</v>
+        <v>0.2316155795078143</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.09020697272523737</v>
+        <v>0.08872816989367616</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6405,22 +6405,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1878137369942906</v>
+        <v>0.1897137369942906</v>
       </c>
       <c r="C63">
-        <v>-81.54120629887376</v>
+        <v>-84.24070917139188</v>
       </c>
       <c r="D63">
-        <v>42.15179370112625</v>
+        <v>41.59529082860813</v>
       </c>
       <c r="E63">
-        <v>95.72300000000001</v>
+        <v>97.86600000000001</v>
       </c>
       <c r="F63">
-        <v>130.723</v>
+        <v>132.866</v>
       </c>
       <c r="G63">
         <v>7.03</v>
@@ -6441,37 +6441,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M63">
-        <v>30.82448340000001</v>
+        <v>31.3298028</v>
       </c>
       <c r="N63">
-        <v>-28.08948340000001</v>
+        <v>-28.5948028</v>
       </c>
       <c r="O63">
-        <v>-5.617896680000001</v>
+        <v>-5.718960560000001</v>
       </c>
       <c r="P63">
-        <v>-22.47158672</v>
+        <v>-22.87584224</v>
       </c>
       <c r="Q63">
-        <v>-20.53158672</v>
+        <v>-20.93584224</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1193031628064716</v>
+        <v>0.1212374565645366</v>
       </c>
       <c r="T63">
-        <v>1.432713454463117</v>
+        <v>1.470416440106884</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.01774563397873522</v>
+        <v>0.0174594140758524</v>
       </c>
       <c r="W63">
-        <v>0.2316155795078143</v>
+        <v>0.231683070160914</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.08872816989367616</v>
+        <v>0.08729707037926193</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6487,22 +6487,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1897137369942906</v>
+        <v>0.1916137369942906</v>
       </c>
       <c r="C64">
-        <v>-84.24070917139188</v>
+        <v>-86.92570922024495</v>
       </c>
       <c r="D64">
-        <v>41.59529082860813</v>
+        <v>41.05329077975505</v>
       </c>
       <c r="E64">
-        <v>97.86600000000001</v>
+        <v>100.009</v>
       </c>
       <c r="F64">
-        <v>132.866</v>
+        <v>135.009</v>
       </c>
       <c r="G64">
         <v>7.03</v>
@@ -6523,37 +6523,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M64">
-        <v>31.3298028</v>
+        <v>31.8351222</v>
       </c>
       <c r="N64">
-        <v>-28.5948028</v>
+        <v>-29.1001222</v>
       </c>
       <c r="O64">
-        <v>-5.718960560000001</v>
+        <v>-5.820024440000001</v>
       </c>
       <c r="P64">
-        <v>-22.87584224</v>
+        <v>-23.28009776</v>
       </c>
       <c r="Q64">
-        <v>-20.93584224</v>
+        <v>-21.34009776</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1212374565645366</v>
+        <v>0.1232763067419565</v>
       </c>
       <c r="T64">
-        <v>1.470416440106884</v>
+        <v>1.510157424974637</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.0174594140758524</v>
+        <v>0.01718228051909284</v>
       </c>
       <c r="W64">
-        <v>0.231683070160914</v>
+        <v>0.2317484182535979</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.08729707037926193</v>
+        <v>0.08591140259546415</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6569,22 +6569,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1916137369942906</v>
+        <v>0.1935137369942906</v>
       </c>
       <c r="C65">
-        <v>-86.92570922024495</v>
+        <v>-89.59676608258368</v>
       </c>
       <c r="D65">
-        <v>41.05329077975505</v>
+        <v>40.52523391741632</v>
       </c>
       <c r="E65">
-        <v>100.009</v>
+        <v>102.152</v>
       </c>
       <c r="F65">
-        <v>135.009</v>
+        <v>137.152</v>
       </c>
       <c r="G65">
         <v>7.03</v>
@@ -6605,37 +6605,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M65">
-        <v>31.8351222</v>
+        <v>32.34044160000001</v>
       </c>
       <c r="N65">
-        <v>-29.1001222</v>
+        <v>-29.60544160000001</v>
       </c>
       <c r="O65">
-        <v>-5.820024440000001</v>
+        <v>-5.921088320000002</v>
       </c>
       <c r="P65">
-        <v>-23.28009776</v>
+        <v>-23.68435328</v>
       </c>
       <c r="Q65">
-        <v>-21.34009776</v>
+        <v>-21.74435328</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1232763067419565</v>
+        <v>0.1254284263736775</v>
       </c>
       <c r="T65">
-        <v>1.510157424974637</v>
+        <v>1.552106242335044</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.01718228051909284</v>
+        <v>0.01691380738598201</v>
       </c>
       <c r="W65">
-        <v>0.2317484182535979</v>
+        <v>0.2318117242183854</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.08591140259546415</v>
+        <v>0.08456903692991002</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6651,22 +6651,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1935137369942906</v>
+        <v>0.1954137369942906</v>
       </c>
       <c r="C66">
-        <v>-89.59676608258368</v>
+        <v>-92.25441096740487</v>
       </c>
       <c r="D66">
-        <v>40.52523391741632</v>
+        <v>40.01058903259515</v>
       </c>
       <c r="E66">
-        <v>102.152</v>
+        <v>104.295</v>
       </c>
       <c r="F66">
-        <v>137.152</v>
+        <v>139.295</v>
       </c>
       <c r="G66">
         <v>7.03</v>
@@ -6687,37 +6687,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M66">
-        <v>32.34044160000001</v>
+        <v>32.845761</v>
       </c>
       <c r="N66">
-        <v>-29.60544160000001</v>
+        <v>-30.110761</v>
       </c>
       <c r="O66">
-        <v>-5.921088320000002</v>
+        <v>-6.022152200000001</v>
       </c>
       <c r="P66">
-        <v>-23.68435328</v>
+        <v>-24.0886088</v>
       </c>
       <c r="Q66">
-        <v>-21.74435328</v>
+        <v>-22.1486088</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1254284263736775</v>
+        <v>0.1277035242700683</v>
       </c>
       <c r="T66">
-        <v>1.552106242335044</v>
+        <v>1.596452134973188</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.01691380738598201</v>
+        <v>0.01665359496465921</v>
       </c>
       <c r="W66">
-        <v>0.2318117242183854</v>
+        <v>0.2318730823073334</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6725,7 +6725,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.08456903692991002</v>
+        <v>0.08326797482329606</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6733,22 +6733,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1954137369942906</v>
+        <v>0.1973137369942906</v>
       </c>
       <c r="C67">
-        <v>-92.25441096740487</v>
+        <v>-94.8991484380132</v>
       </c>
       <c r="D67">
-        <v>40.01058903259515</v>
+        <v>39.50885156198682</v>
       </c>
       <c r="E67">
-        <v>104.295</v>
+        <v>106.438</v>
       </c>
       <c r="F67">
-        <v>139.295</v>
+        <v>141.438</v>
       </c>
       <c r="G67">
         <v>7.03</v>
@@ -6769,37 +6769,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M67">
-        <v>32.845761</v>
+        <v>33.35108040000001</v>
       </c>
       <c r="N67">
-        <v>-30.110761</v>
+        <v>-30.61608040000001</v>
       </c>
       <c r="O67">
-        <v>-6.022152200000001</v>
+        <v>-6.123216080000002</v>
       </c>
       <c r="P67">
-        <v>-24.0886088</v>
+        <v>-24.49286432000001</v>
       </c>
       <c r="Q67">
-        <v>-22.1486088</v>
+        <v>-22.55286432</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1277035242700683</v>
+        <v>0.1301124514544821</v>
       </c>
       <c r="T67">
-        <v>1.596452134973188</v>
+        <v>1.643406609531223</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.01665359496465921</v>
+        <v>0.01640126776822498</v>
       </c>
       <c r="W67">
-        <v>0.2318730823073334</v>
+        <v>0.2319325810602526</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.08326797482329606</v>
+        <v>0.08200633884112485</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6815,22 +6815,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1973137369942906</v>
+        <v>0.1992137369942906</v>
       </c>
       <c r="C68">
-        <v>-94.8991484380132</v>
+        <v>-97.53145806203057</v>
       </c>
       <c r="D68">
-        <v>39.50885156198682</v>
+        <v>39.01954193796946</v>
       </c>
       <c r="E68">
-        <v>106.438</v>
+        <v>108.581</v>
       </c>
       <c r="F68">
-        <v>141.438</v>
+        <v>143.581</v>
       </c>
       <c r="G68">
         <v>7.03</v>
@@ -6851,37 +6851,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M68">
-        <v>33.35108040000001</v>
+        <v>33.85639980000001</v>
       </c>
       <c r="N68">
-        <v>-30.61608040000001</v>
+        <v>-31.12139980000001</v>
       </c>
       <c r="O68">
-        <v>-6.123216080000002</v>
+        <v>-6.224279960000001</v>
       </c>
       <c r="P68">
-        <v>-24.49286432000001</v>
+        <v>-24.89711984000001</v>
       </c>
       <c r="Q68">
-        <v>-22.55286432</v>
+        <v>-22.95711984</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1301124514544821</v>
+        <v>0.1326673742258301</v>
       </c>
       <c r="T68">
-        <v>1.643406609531223</v>
+        <v>1.693206809820048</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.01640126776822498</v>
+        <v>0.01615647272690819</v>
       </c>
       <c r="W68">
-        <v>0.2319325810602526</v>
+        <v>0.2319903037309951</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6889,7 +6889,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.08200633884112485</v>
+        <v>0.08078236363454094</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6897,22 +6897,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1992137369942906</v>
+        <v>0.2011137369942906</v>
       </c>
       <c r="C69">
-        <v>-97.53145806203057</v>
+        <v>-100.1517959402948</v>
       </c>
       <c r="D69">
-        <v>39.01954193796946</v>
+        <v>38.54220405970525</v>
       </c>
       <c r="E69">
-        <v>108.581</v>
+        <v>110.724</v>
       </c>
       <c r="F69">
-        <v>143.581</v>
+        <v>145.724</v>
       </c>
       <c r="G69">
         <v>7.03</v>
@@ -6933,37 +6933,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M69">
-        <v>33.85639980000001</v>
+        <v>34.3617192</v>
       </c>
       <c r="N69">
-        <v>-31.12139980000001</v>
+        <v>-31.6267192</v>
       </c>
       <c r="O69">
-        <v>-6.224279960000001</v>
+        <v>-6.325343840000001</v>
       </c>
       <c r="P69">
-        <v>-24.89711984000001</v>
+        <v>-25.30137536</v>
       </c>
       <c r="Q69">
-        <v>-22.95711984</v>
+        <v>-23.36137536</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1326673742258301</v>
+        <v>0.1353819796703872</v>
       </c>
       <c r="T69">
-        <v>1.693206809820048</v>
+        <v>1.746119522626924</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.01615647272690819</v>
+        <v>0.01591887753974778</v>
       </c>
       <c r="W69">
-        <v>0.2319903037309951</v>
+        <v>0.2320463286761275</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6971,7 +6971,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.08078236363454094</v>
+        <v>0.07959438769873883</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6979,22 +6979,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2011137369942906</v>
+        <v>0.2030137369942906</v>
       </c>
       <c r="C70">
-        <v>-100.1517959402948</v>
+        <v>-102.7605961248938</v>
       </c>
       <c r="D70">
-        <v>38.54220405970525</v>
+        <v>38.0764038751062</v>
       </c>
       <c r="E70">
-        <v>110.724</v>
+        <v>112.867</v>
       </c>
       <c r="F70">
-        <v>145.724</v>
+        <v>147.867</v>
       </c>
       <c r="G70">
         <v>7.03</v>
@@ -7015,37 +7015,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M70">
-        <v>34.3617192</v>
+        <v>34.86703860000001</v>
       </c>
       <c r="N70">
-        <v>-31.6267192</v>
+        <v>-32.13203860000001</v>
       </c>
       <c r="O70">
-        <v>-6.325343840000001</v>
+        <v>-6.426407720000002</v>
       </c>
       <c r="P70">
-        <v>-25.30137536</v>
+        <v>-25.70563088000001</v>
       </c>
       <c r="Q70">
-        <v>-23.36137536</v>
+        <v>-23.76563088000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1353819796703872</v>
+        <v>0.1382717209500771</v>
       </c>
       <c r="T70">
-        <v>1.746119522626924</v>
+        <v>1.802445958840696</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.01591887753974778</v>
+        <v>0.0156881691696065</v>
       </c>
       <c r="W70">
-        <v>0.2320463286761275</v>
+        <v>0.2321007297098068</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.07959438769873883</v>
+        <v>0.07844084584803246</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7061,22 +7061,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2030137369942906</v>
+        <v>0.2049137369942906</v>
       </c>
       <c r="C71">
-        <v>-102.7605961248938</v>
+        <v>-105.358271935602</v>
       </c>
       <c r="D71">
-        <v>38.0764038751062</v>
+        <v>37.62172806439798</v>
       </c>
       <c r="E71">
-        <v>112.867</v>
+        <v>115.01</v>
       </c>
       <c r="F71">
-        <v>147.867</v>
+        <v>150.01</v>
       </c>
       <c r="G71">
         <v>7.03</v>
@@ -7097,37 +7097,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M71">
-        <v>34.86703860000001</v>
+        <v>35.37235800000001</v>
       </c>
       <c r="N71">
-        <v>-32.13203860000001</v>
+        <v>-32.63735800000001</v>
       </c>
       <c r="O71">
-        <v>-6.426407720000002</v>
+        <v>-6.527471600000002</v>
       </c>
       <c r="P71">
-        <v>-25.70563088000001</v>
+        <v>-26.1098864</v>
       </c>
       <c r="Q71">
-        <v>-23.76563088000001</v>
+        <v>-24.1698864</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1382717209500771</v>
+        <v>0.141354111648413</v>
       </c>
       <c r="T71">
-        <v>1.802445958840696</v>
+        <v>1.862527490802053</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.0156881691696065</v>
+        <v>0.01546405246718355</v>
       </c>
       <c r="W71">
-        <v>0.2321007297098068</v>
+        <v>0.2321535764282381</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.07844084584803246</v>
+        <v>0.07732026233591771</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7143,22 +7143,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2049137369942906</v>
+        <v>0.2068137369942906</v>
       </c>
       <c r="C72">
-        <v>-105.358271935602</v>
+        <v>-107.9452171831115</v>
       </c>
       <c r="D72">
-        <v>37.62172806439798</v>
+        <v>37.1777828168885</v>
       </c>
       <c r="E72">
-        <v>115.01</v>
+        <v>117.153</v>
       </c>
       <c r="F72">
-        <v>150.01</v>
+        <v>152.153</v>
       </c>
       <c r="G72">
         <v>7.03</v>
@@ -7179,37 +7179,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M72">
-        <v>35.37235800000001</v>
+        <v>35.8776774</v>
       </c>
       <c r="N72">
-        <v>-32.63735800000001</v>
+        <v>-33.1426774</v>
       </c>
       <c r="O72">
-        <v>-6.527471600000002</v>
+        <v>-6.628535480000001</v>
       </c>
       <c r="P72">
-        <v>-26.1098864</v>
+        <v>-26.51414192</v>
       </c>
       <c r="Q72">
-        <v>-24.1698864</v>
+        <v>-24.57414192</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.141354111648413</v>
+        <v>0.1446490810155997</v>
       </c>
       <c r="T72">
-        <v>1.862527490802053</v>
+        <v>1.926752576691779</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.01546405246718355</v>
+        <v>0.01524624891130773</v>
       </c>
       <c r="W72">
-        <v>0.2321535764282381</v>
+        <v>0.2322049345067136</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7217,7 +7217,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.07732026233591771</v>
+        <v>0.07623124455653862</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7225,22 +7225,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2068137369942906</v>
+        <v>0.2087137369942906</v>
       </c>
       <c r="C73">
-        <v>-107.9452171831115</v>
+        <v>-110.5218073066661</v>
       </c>
       <c r="D73">
-        <v>37.17778281688847</v>
+        <v>36.74419269333391</v>
       </c>
       <c r="E73">
-        <v>117.153</v>
+        <v>119.296</v>
       </c>
       <c r="F73">
-        <v>152.153</v>
+        <v>154.296</v>
       </c>
       <c r="G73">
         <v>7.03</v>
@@ -7261,37 +7261,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M73">
-        <v>35.8776774</v>
+        <v>36.3829968</v>
       </c>
       <c r="N73">
-        <v>-33.1426774</v>
+        <v>-33.6479968</v>
       </c>
       <c r="O73">
-        <v>-6.62853548</v>
+        <v>-6.729599360000001</v>
       </c>
       <c r="P73">
-        <v>-26.51414192</v>
+        <v>-26.91839744</v>
       </c>
       <c r="Q73">
-        <v>-24.57414192</v>
+        <v>-24.97839744</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1446490810155997</v>
+        <v>0.1481794053375854</v>
       </c>
       <c r="T73">
-        <v>1.926752576691778</v>
+        <v>1.995565168716485</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.01524624891130773</v>
+        <v>0.01503449545420623</v>
       </c>
       <c r="W73">
-        <v>0.2322049345067136</v>
+        <v>0.2322548659718982</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.07623124455653862</v>
+        <v>0.07517247727103116</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7307,22 +7307,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2087137369942906</v>
+        <v>0.2106137369942906</v>
       </c>
       <c r="C74">
-        <v>-110.5218073066661</v>
+        <v>-113.0884004330069</v>
       </c>
       <c r="D74">
-        <v>36.74419269333391</v>
+        <v>36.32059956699305</v>
       </c>
       <c r="E74">
-        <v>119.296</v>
+        <v>121.439</v>
       </c>
       <c r="F74">
-        <v>154.296</v>
+        <v>156.439</v>
       </c>
       <c r="G74">
         <v>7.03</v>
@@ -7343,37 +7343,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M74">
-        <v>36.3829968</v>
+        <v>36.8883162</v>
       </c>
       <c r="N74">
-        <v>-33.6479968</v>
+        <v>-34.1533162</v>
       </c>
       <c r="O74">
-        <v>-6.729599360000001</v>
+        <v>-6.83066324</v>
       </c>
       <c r="P74">
-        <v>-26.91839744</v>
+        <v>-27.32265296</v>
       </c>
       <c r="Q74">
-        <v>-24.97839744</v>
+        <v>-25.38265296</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1481794053375854</v>
+        <v>0.1519712351649034</v>
       </c>
       <c r="T74">
-        <v>1.995565168716485</v>
+        <v>2.069474989780058</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.01503449545420623</v>
+        <v>0.01482854346168286</v>
       </c>
       <c r="W74">
-        <v>0.2322548659718982</v>
+        <v>0.2323034294517352</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.07517247727103116</v>
+        <v>0.07414271730841426</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7389,22 +7389,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2106137369942906</v>
+        <v>0.2125137369942906</v>
       </c>
       <c r="C75">
-        <v>-113.0884004330069</v>
+        <v>-115.6453383629068</v>
       </c>
       <c r="D75">
-        <v>36.32059956699305</v>
+        <v>35.90666163709317</v>
       </c>
       <c r="E75">
-        <v>121.439</v>
+        <v>123.582</v>
       </c>
       <c r="F75">
-        <v>156.439</v>
+        <v>158.582</v>
       </c>
       <c r="G75">
         <v>7.03</v>
@@ -7425,37 +7425,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M75">
-        <v>36.8883162</v>
+        <v>37.3936356</v>
       </c>
       <c r="N75">
-        <v>-34.1533162</v>
+        <v>-34.6586356</v>
       </c>
       <c r="O75">
-        <v>-6.83066324</v>
+        <v>-6.931727120000001</v>
       </c>
       <c r="P75">
-        <v>-27.32265296</v>
+        <v>-27.72690848</v>
       </c>
       <c r="Q75">
-        <v>-25.38265296</v>
+        <v>-25.78690848</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.1519712351649034</v>
+        <v>0.1560547442097073</v>
       </c>
       <c r="T75">
-        <v>2.069474989780058</v>
+        <v>2.149070181694676</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.01482854346168286</v>
+        <v>0.01462815773922769</v>
       </c>
       <c r="W75">
-        <v>0.2323034294517352</v>
+        <v>0.2323506804050901</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7463,7 +7463,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.07414271730841426</v>
+        <v>0.07314078869613838</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7471,22 +7471,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2125137369942906</v>
+        <v>0.2144137369942906</v>
       </c>
       <c r="C76">
-        <v>-115.6453383629068</v>
+        <v>-118.1929474910041</v>
       </c>
       <c r="D76">
-        <v>35.90666163709317</v>
+        <v>35.50205250899593</v>
       </c>
       <c r="E76">
-        <v>123.582</v>
+        <v>125.725</v>
       </c>
       <c r="F76">
-        <v>158.582</v>
+        <v>160.725</v>
       </c>
       <c r="G76">
         <v>7.03</v>
@@ -7507,37 +7507,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M76">
-        <v>37.3936356</v>
+        <v>37.89895500000001</v>
       </c>
       <c r="N76">
-        <v>-34.6586356</v>
+        <v>-35.16395500000001</v>
       </c>
       <c r="O76">
-        <v>-6.931727120000001</v>
+        <v>-7.032791000000002</v>
       </c>
       <c r="P76">
-        <v>-27.72690848</v>
+        <v>-28.13116400000001</v>
       </c>
       <c r="Q76">
-        <v>-25.78690848</v>
+        <v>-26.191164</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1560547442097073</v>
+        <v>0.1604649339780956</v>
       </c>
       <c r="T76">
-        <v>2.149070181694676</v>
+        <v>2.235032988962463</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.01462815773922769</v>
+        <v>0.01443311563603798</v>
       </c>
       <c r="W76">
-        <v>0.2323506804050901</v>
+        <v>0.2323966713330222</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.07314078869613838</v>
+        <v>0.07216557818018987</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7553,22 +7553,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2144137369942906</v>
+        <v>0.2163137369942906</v>
       </c>
       <c r="C77">
-        <v>-118.1929474910041</v>
+        <v>-120.7315396641399</v>
       </c>
       <c r="D77">
-        <v>35.50205250899593</v>
+        <v>35.10646033586008</v>
       </c>
       <c r="E77">
-        <v>125.725</v>
+        <v>127.868</v>
       </c>
       <c r="F77">
-        <v>160.725</v>
+        <v>162.868</v>
       </c>
       <c r="G77">
         <v>7.03</v>
@@ -7589,37 +7589,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M77">
-        <v>37.89895500000001</v>
+        <v>38.40427440000001</v>
       </c>
       <c r="N77">
-        <v>-35.16395500000001</v>
+        <v>-35.66927440000001</v>
       </c>
       <c r="O77">
-        <v>-7.032791000000002</v>
+        <v>-7.133854880000001</v>
       </c>
       <c r="P77">
-        <v>-28.13116400000001</v>
+        <v>-28.53541952</v>
       </c>
       <c r="Q77">
-        <v>-26.191164</v>
+        <v>-26.59541952</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1604649339780956</v>
+        <v>0.1652426395605163</v>
       </c>
       <c r="T77">
-        <v>2.235032988962463</v>
+        <v>2.328159363502566</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.01443311563603798</v>
+        <v>0.01424320621977433</v>
       </c>
       <c r="W77">
-        <v>0.2323966713330222</v>
+        <v>0.2324414519733772</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.07216557818018987</v>
+        <v>0.07121603109887165</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7635,22 +7635,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2163137369942906</v>
+        <v>0.2182137369942906</v>
       </c>
       <c r="C78">
-        <v>-120.7315396641399</v>
+        <v>-123.2614129829425</v>
       </c>
       <c r="D78">
-        <v>35.10646033586008</v>
+        <v>34.71958701705748</v>
       </c>
       <c r="E78">
-        <v>127.868</v>
+        <v>130.011</v>
       </c>
       <c r="F78">
-        <v>162.868</v>
+        <v>165.011</v>
       </c>
       <c r="G78">
         <v>7.03</v>
@@ -7671,37 +7671,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M78">
-        <v>38.40427440000001</v>
+        <v>38.90959380000001</v>
       </c>
       <c r="N78">
-        <v>-35.66927440000001</v>
+        <v>-36.17459380000001</v>
       </c>
       <c r="O78">
-        <v>-7.133854880000001</v>
+        <v>-7.234918760000003</v>
       </c>
       <c r="P78">
-        <v>-28.53541952</v>
+        <v>-28.93967504000001</v>
       </c>
       <c r="Q78">
-        <v>-26.59541952</v>
+        <v>-26.99967504000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1652426395605163</v>
+        <v>0.1704357978022779</v>
       </c>
       <c r="T78">
-        <v>2.328159363502566</v>
+        <v>2.429383683654851</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.01424320621977433</v>
+        <v>0.01405822951562141</v>
       </c>
       <c r="W78">
-        <v>0.2324414519733772</v>
+        <v>0.2324850694802165</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.07121603109887165</v>
+        <v>0.07029114757810706</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7717,22 +7717,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2182137369942906</v>
+        <v>0.2201137369942906</v>
       </c>
       <c r="C79">
-        <v>-123.2614129829425</v>
+        <v>-125.7828525509874</v>
       </c>
       <c r="D79">
-        <v>34.71958701705748</v>
+        <v>34.34114744901258</v>
       </c>
       <c r="E79">
-        <v>130.011</v>
+        <v>132.154</v>
       </c>
       <c r="F79">
-        <v>165.011</v>
+        <v>167.154</v>
       </c>
       <c r="G79">
         <v>7.03</v>
@@ -7753,37 +7753,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M79">
-        <v>38.90959380000001</v>
+        <v>39.41491320000001</v>
       </c>
       <c r="N79">
-        <v>-36.17459380000001</v>
+        <v>-36.67991320000001</v>
       </c>
       <c r="O79">
-        <v>-7.234918760000003</v>
+        <v>-7.335982640000002</v>
       </c>
       <c r="P79">
-        <v>-28.93967504000001</v>
+        <v>-29.34393056000001</v>
       </c>
       <c r="Q79">
-        <v>-26.99967504000001</v>
+        <v>-27.40393056000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1704357978022779</v>
+        <v>0.1761010613387451</v>
       </c>
       <c r="T79">
-        <v>2.429383683654851</v>
+        <v>2.539810214730072</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.01405822951562141</v>
+        <v>0.01387799580388267</v>
       </c>
       <c r="W79">
-        <v>0.2324850694802165</v>
+        <v>0.2325275685894445</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.07029114757810706</v>
+        <v>0.06938997901941335</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7799,22 +7799,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2201137369942906</v>
+        <v>0.2220137369942906</v>
       </c>
       <c r="C80">
-        <v>-125.7828525509874</v>
+        <v>-128.2961311754924</v>
       </c>
       <c r="D80">
-        <v>34.34114744901258</v>
+        <v>33.97086882450764</v>
       </c>
       <c r="E80">
-        <v>132.154</v>
+        <v>134.297</v>
       </c>
       <c r="F80">
-        <v>167.154</v>
+        <v>169.297</v>
       </c>
       <c r="G80">
         <v>7.03</v>
@@ -7835,37 +7835,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M80">
-        <v>39.41491320000001</v>
+        <v>39.92023260000001</v>
       </c>
       <c r="N80">
-        <v>-36.67991320000001</v>
+        <v>-37.18523260000001</v>
       </c>
       <c r="O80">
-        <v>-7.335982640000002</v>
+        <v>-7.437046520000002</v>
       </c>
       <c r="P80">
-        <v>-29.34393056000001</v>
+        <v>-29.74818608</v>
       </c>
       <c r="Q80">
-        <v>-27.40393056000001</v>
+        <v>-27.80818608</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1761010613387451</v>
+        <v>0.1823058737834472</v>
       </c>
       <c r="T80">
-        <v>2.539810214730072</v>
+        <v>2.660753558288647</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.01387799580388267</v>
+        <v>0.01370232497092213</v>
       </c>
       <c r="W80">
-        <v>0.2325275685894445</v>
+        <v>0.2325689917718566</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7873,7 +7873,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.06938997901941335</v>
+        <v>0.06851162485461071</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7881,22 +7881,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2220137369942906</v>
+        <v>0.2239137369942906</v>
       </c>
       <c r="C81">
-        <v>-128.2961311754924</v>
+        <v>-130.8015100231645</v>
       </c>
       <c r="D81">
-        <v>33.97086882450764</v>
+        <v>33.60848997683556</v>
       </c>
       <c r="E81">
-        <v>134.297</v>
+        <v>136.44</v>
       </c>
       <c r="F81">
-        <v>169.297</v>
+        <v>171.44</v>
       </c>
       <c r="G81">
         <v>7.03</v>
@@ -7917,37 +7917,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M81">
-        <v>39.92023260000001</v>
+        <v>40.42555200000001</v>
       </c>
       <c r="N81">
-        <v>-37.18523260000001</v>
+        <v>-37.69055200000001</v>
       </c>
       <c r="O81">
-        <v>-7.437046520000002</v>
+        <v>-7.538110400000003</v>
       </c>
       <c r="P81">
-        <v>-29.74818608</v>
+        <v>-30.15244160000001</v>
       </c>
       <c r="Q81">
-        <v>-27.80818608</v>
+        <v>-28.21244160000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1823058737834472</v>
+        <v>0.1891311674726196</v>
       </c>
       <c r="T81">
-        <v>2.660753558288647</v>
+        <v>2.793791236203079</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.01370232497092213</v>
+        <v>0.01353104590878561</v>
       </c>
       <c r="W81">
-        <v>0.2325689917718566</v>
+        <v>0.2326093793747084</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.06851162485461071</v>
+        <v>0.067655229543928</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7963,22 +7963,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2239137369942906</v>
+        <v>0.2258137369942906</v>
       </c>
       <c r="C82">
-        <v>-130.8015100231645</v>
+        <v>-133.2992392345136</v>
       </c>
       <c r="D82">
-        <v>33.60848997683556</v>
+        <v>33.25376076548644</v>
       </c>
       <c r="E82">
-        <v>136.44</v>
+        <v>138.583</v>
       </c>
       <c r="F82">
-        <v>171.44</v>
+        <v>173.583</v>
       </c>
       <c r="G82">
         <v>7.03</v>
@@ -7999,37 +7999,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M82">
-        <v>40.42555200000001</v>
+        <v>40.93087140000001</v>
       </c>
       <c r="N82">
-        <v>-37.69055200000001</v>
+        <v>-38.19587140000001</v>
       </c>
       <c r="O82">
-        <v>-7.538110400000003</v>
+        <v>-7.639174280000002</v>
       </c>
       <c r="P82">
-        <v>-30.15244160000001</v>
+        <v>-30.55669712000001</v>
       </c>
       <c r="Q82">
-        <v>-28.21244160000001</v>
+        <v>-28.61669712</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.1891311674726196</v>
+        <v>0.1966749131290733</v>
       </c>
       <c r="T82">
-        <v>2.793791236203079</v>
+        <v>2.940832880213768</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.01353104590878561</v>
+        <v>0.01336399595929443</v>
       </c>
       <c r="W82">
-        <v>0.2326093793747084</v>
+        <v>0.2326487697527984</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8037,7 +8037,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.067655229543928</v>
+        <v>0.06681997979647214</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8045,22 +8045,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2258137369942906</v>
+        <v>0.2277137369942906</v>
       </c>
       <c r="C83">
-        <v>-133.2992392345136</v>
+        <v>-135.7895584996684</v>
       </c>
       <c r="D83">
-        <v>33.25376076548644</v>
+        <v>32.90644150033164</v>
       </c>
       <c r="E83">
-        <v>138.583</v>
+        <v>140.726</v>
       </c>
       <c r="F83">
-        <v>173.583</v>
+        <v>175.726</v>
       </c>
       <c r="G83">
         <v>7.03</v>
@@ -8081,37 +8081,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M83">
-        <v>40.93087140000001</v>
+        <v>41.43619080000001</v>
       </c>
       <c r="N83">
-        <v>-38.19587140000001</v>
+        <v>-38.70119080000001</v>
       </c>
       <c r="O83">
-        <v>-7.639174280000002</v>
+        <v>-7.740238160000001</v>
       </c>
       <c r="P83">
-        <v>-30.55669712000001</v>
+        <v>-30.96095264000001</v>
       </c>
       <c r="Q83">
-        <v>-28.61669712</v>
+        <v>-29.02095264</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1966749131290733</v>
+        <v>0.2050568527473551</v>
       </c>
       <c r="T83">
-        <v>2.940832880213768</v>
+        <v>3.104212484670088</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.01336399595929443</v>
+        <v>0.01320102039881523</v>
       </c>
       <c r="W83">
-        <v>0.2326487697527984</v>
+        <v>0.2326871993899594</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8119,7 +8119,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.06681997979647214</v>
+        <v>0.06600510199407617</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8127,22 +8127,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2277137369942906</v>
+        <v>0.2296137369942906</v>
       </c>
       <c r="C84">
-        <v>-135.7895584996684</v>
+        <v>-138.2726975984811</v>
       </c>
       <c r="D84">
-        <v>32.90644150033164</v>
+        <v>32.56630240151894</v>
       </c>
       <c r="E84">
-        <v>140.726</v>
+        <v>142.869</v>
       </c>
       <c r="F84">
-        <v>175.726</v>
+        <v>177.869</v>
       </c>
       <c r="G84">
         <v>7.03</v>
@@ -8163,37 +8163,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M84">
-        <v>41.43619080000001</v>
+        <v>41.94151020000001</v>
       </c>
       <c r="N84">
-        <v>-38.70119080000001</v>
+        <v>-39.20651020000001</v>
       </c>
       <c r="O84">
-        <v>-7.740238160000001</v>
+        <v>-7.841302040000002</v>
       </c>
       <c r="P84">
-        <v>-30.96095264000001</v>
+        <v>-31.36520816000001</v>
       </c>
       <c r="Q84">
-        <v>-29.02095264</v>
+        <v>-29.42520816000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2050568527473551</v>
+        <v>0.2144249029089643</v>
       </c>
       <c r="T84">
-        <v>3.104212484670088</v>
+        <v>3.286813219062447</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.01320102039881523</v>
+        <v>0.01304197196027528</v>
       </c>
       <c r="W84">
-        <v>0.2326871993899594</v>
+        <v>0.2327247030117671</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8201,7 +8201,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.06600510199407617</v>
+        <v>0.06520985980137639</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8209,22 +8209,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2296137369942906</v>
+        <v>0.2315137369942906</v>
       </c>
       <c r="C85">
-        <v>-138.2726975984811</v>
+        <v>-140.7488769074774</v>
       </c>
       <c r="D85">
-        <v>32.56630240151894</v>
+        <v>32.23312309252263</v>
       </c>
       <c r="E85">
-        <v>142.869</v>
+        <v>145.012</v>
       </c>
       <c r="F85">
-        <v>177.869</v>
+        <v>180.012</v>
       </c>
       <c r="G85">
         <v>7.03</v>
@@ -8245,37 +8245,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M85">
-        <v>41.94151020000001</v>
+        <v>42.44682960000001</v>
       </c>
       <c r="N85">
-        <v>-39.20651020000001</v>
+        <v>-39.71182960000001</v>
       </c>
       <c r="O85">
-        <v>-7.841302040000002</v>
+        <v>-7.942365920000002</v>
       </c>
       <c r="P85">
-        <v>-31.36520816000001</v>
+        <v>-31.76946368000001</v>
       </c>
       <c r="Q85">
-        <v>-29.42520816000001</v>
+        <v>-29.82946368000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2144249029089643</v>
+        <v>0.2249639593407746</v>
       </c>
       <c r="T85">
-        <v>3.286813219062447</v>
+        <v>3.492239045253851</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.01304197196027528</v>
+        <v>0.01288671038931963</v>
       </c>
       <c r="W85">
-        <v>0.2327247030117671</v>
+        <v>0.2327613136901984</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.06520985980137639</v>
+        <v>0.06443355194659817</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8291,22 +8291,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2315137369942906</v>
+        <v>0.2334137369942906</v>
       </c>
       <c r="C86">
-        <v>-140.7488769074774</v>
+        <v>-143.2183078760032</v>
       </c>
       <c r="D86">
-        <v>32.2331230925226</v>
+        <v>31.90669212399682</v>
       </c>
       <c r="E86">
-        <v>145.012</v>
+        <v>147.155</v>
       </c>
       <c r="F86">
-        <v>180.012</v>
+        <v>182.155</v>
       </c>
       <c r="G86">
         <v>7.03</v>
@@ -8327,37 +8327,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M86">
-        <v>42.4468296</v>
+        <v>42.952149</v>
       </c>
       <c r="N86">
-        <v>-39.7118296</v>
+        <v>-40.217149</v>
       </c>
       <c r="O86">
-        <v>-7.94236592</v>
+        <v>-8.0434298</v>
       </c>
       <c r="P86">
-        <v>-31.76946368</v>
+        <v>-32.1737192</v>
       </c>
       <c r="Q86">
-        <v>-29.82946368</v>
+        <v>-30.2337192</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.2249639593407744</v>
+        <v>0.2369082232968261</v>
       </c>
       <c r="T86">
-        <v>3.492239045253848</v>
+        <v>3.725054981604105</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.01288671038931963</v>
+        <v>0.01273510203179822</v>
       </c>
       <c r="W86">
-        <v>0.2327613136901984</v>
+        <v>0.232797062940902</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8365,7 +8365,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.06443355194659817</v>
+        <v>0.06367551015899109</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8373,22 +8373,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2334137369942906</v>
+        <v>0.2353137369942906</v>
       </c>
       <c r="C87">
-        <v>-143.2183078760032</v>
+        <v>-145.6811934737286</v>
       </c>
       <c r="D87">
-        <v>31.90669212399682</v>
+        <v>31.58680652627136</v>
       </c>
       <c r="E87">
-        <v>147.155</v>
+        <v>149.298</v>
       </c>
       <c r="F87">
-        <v>182.155</v>
+        <v>184.298</v>
       </c>
       <c r="G87">
         <v>7.03</v>
@@ -8409,37 +8409,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M87">
-        <v>42.952149</v>
+        <v>43.4574684</v>
       </c>
       <c r="N87">
-        <v>-40.217149</v>
+        <v>-40.7224684</v>
       </c>
       <c r="O87">
-        <v>-8.0434298</v>
+        <v>-8.144493680000002</v>
       </c>
       <c r="P87">
-        <v>-32.1737192</v>
+        <v>-32.57797472</v>
       </c>
       <c r="Q87">
-        <v>-30.2337192</v>
+        <v>-30.63797472</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2369082232968261</v>
+        <v>0.2505588106751708</v>
       </c>
       <c r="T87">
-        <v>3.725054981604105</v>
+        <v>3.991130337432969</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.01273510203179822</v>
+        <v>0.01258701945003312</v>
       </c>
       <c r="W87">
-        <v>0.232797062940902</v>
+        <v>0.2328319808136822</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8447,7 +8447,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.06367551015899109</v>
+        <v>0.06293509725016566</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8455,22 +8455,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2353137369942906</v>
+        <v>0.2372137369942906</v>
       </c>
       <c r="C88">
-        <v>-145.6811934737286</v>
+        <v>-148.1377286115004</v>
       </c>
       <c r="D88">
-        <v>31.58680652627136</v>
+        <v>31.27327138849959</v>
       </c>
       <c r="E88">
-        <v>149.298</v>
+        <v>151.441</v>
       </c>
       <c r="F88">
-        <v>184.298</v>
+        <v>186.441</v>
       </c>
       <c r="G88">
         <v>7.03</v>
@@ -8491,37 +8491,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M88">
-        <v>43.4574684</v>
+        <v>43.9627878</v>
       </c>
       <c r="N88">
-        <v>-40.7224684</v>
+        <v>-41.2277878</v>
       </c>
       <c r="O88">
-        <v>-8.144493680000002</v>
+        <v>-8.24555756</v>
       </c>
       <c r="P88">
-        <v>-32.57797472</v>
+        <v>-32.98223024</v>
       </c>
       <c r="Q88">
-        <v>-30.63797472</v>
+        <v>-31.04223024</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.2505588106751708</v>
+        <v>0.2663094884194147</v>
       </c>
       <c r="T88">
-        <v>3.991130337432969</v>
+        <v>4.298140363389352</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.01258701945003312</v>
+        <v>0.01244234106554998</v>
       </c>
       <c r="W88">
-        <v>0.2328319808136822</v>
+        <v>0.2328660959767433</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.06293509725016566</v>
+        <v>0.06221170532774989</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8537,22 +8537,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2372137369942906</v>
+        <v>0.2391137369942906</v>
       </c>
       <c r="C89">
-        <v>-148.1377286115004</v>
+        <v>-150.588100537376</v>
       </c>
       <c r="D89">
-        <v>31.27327138849959</v>
+        <v>30.96589946262401</v>
       </c>
       <c r="E89">
-        <v>151.441</v>
+        <v>153.584</v>
       </c>
       <c r="F89">
-        <v>186.441</v>
+        <v>188.584</v>
       </c>
       <c r="G89">
         <v>7.03</v>
@@ -8573,37 +8573,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M89">
-        <v>43.9627878</v>
+        <v>44.46810720000001</v>
       </c>
       <c r="N89">
-        <v>-41.2277878</v>
+        <v>-41.73310720000001</v>
       </c>
       <c r="O89">
-        <v>-8.24555756</v>
+        <v>-8.346621440000002</v>
       </c>
       <c r="P89">
-        <v>-32.98223024</v>
+        <v>-33.38648576000001</v>
       </c>
       <c r="Q89">
-        <v>-31.04223024</v>
+        <v>-31.44648576000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2663094884194147</v>
+        <v>0.2846852791210326</v>
       </c>
       <c r="T89">
-        <v>4.298140363389352</v>
+        <v>4.656318727005131</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.01244234106554998</v>
+        <v>0.01230095082616874</v>
       </c>
       <c r="W89">
-        <v>0.2328660959767433</v>
+        <v>0.2328994357951894</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.06221170532774989</v>
+        <v>0.06150475413084366</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8619,22 +8619,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2391137369942906</v>
+        <v>0.2410137369942906</v>
       </c>
       <c r="C90">
-        <v>-150.588100537376</v>
+        <v>-153.0324892095303</v>
       </c>
       <c r="D90">
-        <v>30.96589946262401</v>
+        <v>30.66451079046968</v>
       </c>
       <c r="E90">
-        <v>153.584</v>
+        <v>155.727</v>
       </c>
       <c r="F90">
-        <v>188.584</v>
+        <v>190.727</v>
       </c>
       <c r="G90">
         <v>7.03</v>
@@ -8655,37 +8655,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M90">
-        <v>44.46810720000001</v>
+        <v>44.9734266</v>
       </c>
       <c r="N90">
-        <v>-41.73310720000001</v>
+        <v>-42.2384266</v>
       </c>
       <c r="O90">
-        <v>-8.346621440000002</v>
+        <v>-8.447685320000001</v>
       </c>
       <c r="P90">
-        <v>-33.38648576000001</v>
+        <v>-33.79074128000001</v>
       </c>
       <c r="Q90">
-        <v>-31.44648576000001</v>
+        <v>-31.85074128</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2846852791210326</v>
+        <v>0.3064021226774901</v>
       </c>
       <c r="T90">
-        <v>4.656318727005131</v>
+        <v>5.079620429460143</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.01230095082616874</v>
+        <v>0.01216273789553762</v>
       </c>
       <c r="W90">
-        <v>0.2328994357951894</v>
+        <v>0.2329320264042322</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.06150475413084366</v>
+        <v>0.06081368947768817</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8701,22 +8701,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2410137369942906</v>
+        <v>0.2429137369942906</v>
       </c>
       <c r="C91">
-        <v>-153.0324892095303</v>
+        <v>-155.4710676475951</v>
       </c>
       <c r="D91">
-        <v>30.66451079046968</v>
+        <v>30.36893235240487</v>
       </c>
       <c r="E91">
-        <v>155.727</v>
+        <v>157.87</v>
       </c>
       <c r="F91">
-        <v>190.727</v>
+        <v>192.87</v>
       </c>
       <c r="G91">
         <v>7.03</v>
@@ -8737,37 +8737,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M91">
-        <v>44.9734266</v>
+        <v>45.478746</v>
       </c>
       <c r="N91">
-        <v>-42.2384266</v>
+        <v>-42.743746</v>
       </c>
       <c r="O91">
-        <v>-8.447685320000001</v>
+        <v>-8.548749200000001</v>
       </c>
       <c r="P91">
-        <v>-33.79074128000001</v>
+        <v>-34.1949968</v>
       </c>
       <c r="Q91">
-        <v>-31.85074128</v>
+        <v>-32.2549968</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3064021226774901</v>
+        <v>0.3324623349452391</v>
       </c>
       <c r="T91">
-        <v>5.079620429460143</v>
+        <v>5.587582472406158</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.01216273789553762</v>
+        <v>0.01202759636336499</v>
       </c>
       <c r="W91">
-        <v>0.2329320264042322</v>
+        <v>0.2329638927775185</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8775,7 +8775,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.06081368947768817</v>
+        <v>0.06013798181682495</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8783,22 +8783,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2429137369942906</v>
+        <v>0.2448137369942906</v>
       </c>
       <c r="C92">
-        <v>-155.4710676475951</v>
+        <v>-157.9040022638735</v>
       </c>
       <c r="D92">
-        <v>30.36893235240487</v>
+        <v>30.07899773612647</v>
       </c>
       <c r="E92">
-        <v>157.87</v>
+        <v>160.013</v>
       </c>
       <c r="F92">
-        <v>192.87</v>
+        <v>195.013</v>
       </c>
       <c r="G92">
         <v>7.03</v>
@@ -8819,37 +8819,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M92">
-        <v>45.478746</v>
+        <v>45.98406540000001</v>
       </c>
       <c r="N92">
-        <v>-42.743746</v>
+        <v>-43.24906540000001</v>
       </c>
       <c r="O92">
-        <v>-8.548749200000001</v>
+        <v>-8.649813080000001</v>
       </c>
       <c r="P92">
-        <v>-34.1949968</v>
+        <v>-34.59925232000001</v>
       </c>
       <c r="Q92">
-        <v>-32.2549968</v>
+        <v>-32.65925232000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.3324623349452391</v>
+        <v>0.3643137054947102</v>
       </c>
       <c r="T92">
-        <v>5.587582472406158</v>
+        <v>6.208424969340176</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.01202759636336499</v>
+        <v>0.01189542497475658</v>
       </c>
       <c r="W92">
-        <v>0.2329638927775185</v>
+        <v>0.2329950587909524</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8857,7 +8857,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.06013798181682495</v>
+        <v>0.05947712487378287</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8865,22 +8865,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2448137369942906</v>
+        <v>0.2467137369942906</v>
       </c>
       <c r="C93">
-        <v>-157.9040022638735</v>
+        <v>-160.3314531757605</v>
       </c>
       <c r="D93">
-        <v>30.07899773612647</v>
+        <v>29.79454682423954</v>
       </c>
       <c r="E93">
-        <v>160.013</v>
+        <v>162.156</v>
       </c>
       <c r="F93">
-        <v>195.013</v>
+        <v>197.156</v>
       </c>
       <c r="G93">
         <v>7.03</v>
@@ -8901,37 +8901,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M93">
-        <v>45.98406540000001</v>
+        <v>46.4893848</v>
       </c>
       <c r="N93">
-        <v>-43.24906540000001</v>
+        <v>-43.7543848</v>
       </c>
       <c r="O93">
-        <v>-8.649813080000001</v>
+        <v>-8.750876960000001</v>
       </c>
       <c r="P93">
-        <v>-34.59925232000001</v>
+        <v>-35.00350784</v>
       </c>
       <c r="Q93">
-        <v>-32.65925232000001</v>
+        <v>-33.06350784000001</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3643137054947102</v>
+        <v>0.4041279186815491</v>
       </c>
       <c r="T93">
-        <v>6.208424969340176</v>
+        <v>6.984478090507701</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.01189542497475658</v>
+        <v>0.01176612687720488</v>
       </c>
       <c r="W93">
-        <v>0.2329950587909524</v>
+        <v>0.2330255472823551</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.05947712487378287</v>
+        <v>0.05883063438602443</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8947,22 +8947,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2467137369942906</v>
+        <v>0.2486137369942906</v>
       </c>
       <c r="C94">
-        <v>-160.3314531757605</v>
+        <v>-162.7535745006028</v>
       </c>
       <c r="D94">
-        <v>29.79454682423954</v>
+        <v>29.51542549939726</v>
       </c>
       <c r="E94">
-        <v>162.156</v>
+        <v>164.299</v>
       </c>
       <c r="F94">
-        <v>197.156</v>
+        <v>199.299</v>
       </c>
       <c r="G94">
         <v>7.03</v>
@@ -8983,37 +8983,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M94">
-        <v>46.4893848</v>
+        <v>46.99470420000001</v>
       </c>
       <c r="N94">
-        <v>-43.7543848</v>
+        <v>-44.25970420000001</v>
       </c>
       <c r="O94">
-        <v>-8.750876960000001</v>
+        <v>-8.851940840000003</v>
       </c>
       <c r="P94">
-        <v>-35.00350784</v>
+        <v>-35.40776336</v>
       </c>
       <c r="Q94">
-        <v>-33.06350784000001</v>
+        <v>-33.46776336000001</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.4041279186815491</v>
+        <v>0.4553176213503419</v>
       </c>
       <c r="T94">
-        <v>6.984478090507701</v>
+        <v>7.982260674865945</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.01176612687720488</v>
+        <v>0.0116396093839016</v>
       </c>
       <c r="W94">
-        <v>0.2330255472823551</v>
+        <v>0.233055380107276</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.05883063438602443</v>
+        <v>0.05819804691950803</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9029,22 +9029,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2486137369942906</v>
+        <v>0.2505137369942906</v>
       </c>
       <c r="C95">
-        <v>-162.7535745006028</v>
+        <v>-165.1705146341387</v>
       </c>
       <c r="D95">
-        <v>29.51542549939726</v>
+        <v>29.24148536586134</v>
       </c>
       <c r="E95">
-        <v>164.299</v>
+        <v>166.442</v>
       </c>
       <c r="F95">
-        <v>199.299</v>
+        <v>201.442</v>
       </c>
       <c r="G95">
         <v>7.03</v>
@@ -9065,37 +9065,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M95">
-        <v>46.99470420000001</v>
+        <v>47.50002360000001</v>
       </c>
       <c r="N95">
-        <v>-44.25970420000001</v>
+        <v>-44.76502360000001</v>
       </c>
       <c r="O95">
-        <v>-8.851940840000003</v>
+        <v>-8.953004720000003</v>
       </c>
       <c r="P95">
-        <v>-35.40776336</v>
+        <v>-35.81201888000001</v>
       </c>
       <c r="Q95">
-        <v>-33.46776336000001</v>
+        <v>-33.87201888000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.4553176213503419</v>
+        <v>0.5235705582420657</v>
       </c>
       <c r="T95">
-        <v>7.982260674865945</v>
+        <v>9.312637454010272</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.0116396093839016</v>
+        <v>0.01151578375215796</v>
       </c>
       <c r="W95">
-        <v>0.233055380107276</v>
+        <v>0.2330845781912411</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9103,7 +9103,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.05819804691950803</v>
+        <v>0.0575789187607898</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9111,22 +9111,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2505137369942906</v>
+        <v>0.2524137369942906</v>
       </c>
       <c r="C96">
-        <v>-165.1705146341387</v>
+        <v>-167.5824165135751</v>
       </c>
       <c r="D96">
-        <v>29.24148536586134</v>
+        <v>28.97258348642497</v>
       </c>
       <c r="E96">
-        <v>166.442</v>
+        <v>168.585</v>
       </c>
       <c r="F96">
-        <v>201.442</v>
+        <v>203.585</v>
       </c>
       <c r="G96">
         <v>7.03</v>
@@ -9147,37 +9147,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M96">
-        <v>47.50002360000001</v>
+        <v>48.00534300000001</v>
       </c>
       <c r="N96">
-        <v>-44.76502360000001</v>
+        <v>-45.27034300000001</v>
       </c>
       <c r="O96">
-        <v>-8.953004720000003</v>
+        <v>-9.054068600000003</v>
       </c>
       <c r="P96">
-        <v>-35.81201888000001</v>
+        <v>-36.21627440000001</v>
       </c>
       <c r="Q96">
-        <v>-33.87201888000001</v>
+        <v>-34.27627440000001</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.5235705582420657</v>
+        <v>0.619124669890479</v>
       </c>
       <c r="T96">
-        <v>9.312637454010272</v>
+        <v>11.17516494481233</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.01151578375215796</v>
+        <v>0.01139456497581946</v>
       </c>
       <c r="W96">
-        <v>0.2330845781912411</v>
+        <v>0.2331131615787018</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9185,7 +9185,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.0575789187607898</v>
+        <v>0.05697282487909727</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9193,22 +9193,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2524137369942906</v>
+        <v>0.2543137369942906</v>
       </c>
       <c r="C97">
-        <v>-167.5824165135751</v>
+        <v>-169.9894178662807</v>
       </c>
       <c r="D97">
-        <v>28.97258348642497</v>
+        <v>28.70858213371929</v>
       </c>
       <c r="E97">
-        <v>168.585</v>
+        <v>170.728</v>
       </c>
       <c r="F97">
-        <v>203.585</v>
+        <v>205.728</v>
       </c>
       <c r="G97">
         <v>7.03</v>
@@ -9229,37 +9229,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M97">
-        <v>48.00534300000001</v>
+        <v>48.51066240000001</v>
       </c>
       <c r="N97">
-        <v>-45.27034300000001</v>
+        <v>-45.77566240000001</v>
       </c>
       <c r="O97">
-        <v>-9.054068600000003</v>
+        <v>-9.155132480000002</v>
       </c>
       <c r="P97">
-        <v>-36.21627440000001</v>
+        <v>-36.62052992000001</v>
       </c>
       <c r="Q97">
-        <v>-34.27627440000001</v>
+        <v>-34.68052992000001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.619124669890479</v>
+        <v>0.7624558373630991</v>
       </c>
       <c r="T97">
-        <v>11.17516494481233</v>
+        <v>13.96895618101542</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.01139456497581946</v>
+        <v>0.01127587159065467</v>
       </c>
       <c r="W97">
-        <v>0.2331131615787018</v>
+        <v>0.2331411494789236</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9267,7 +9267,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.05697282487909727</v>
+        <v>0.05637935795327331</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9275,22 +9275,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2543137369942906</v>
+        <v>0.2562137369942906</v>
       </c>
       <c r="C98">
-        <v>-169.9894178662807</v>
+        <v>-172.3916514450063</v>
       </c>
       <c r="D98">
-        <v>28.70858213371929</v>
+        <v>28.44934855499366</v>
       </c>
       <c r="E98">
-        <v>170.728</v>
+        <v>172.871</v>
       </c>
       <c r="F98">
-        <v>205.728</v>
+        <v>207.871</v>
       </c>
       <c r="G98">
         <v>7.03</v>
@@ -9311,37 +9311,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M98">
-        <v>48.5106624</v>
+        <v>49.01598180000001</v>
       </c>
       <c r="N98">
-        <v>-45.7756624</v>
+        <v>-46.28098180000001</v>
       </c>
       <c r="O98">
-        <v>-9.155132480000001</v>
+        <v>-9.256196360000002</v>
       </c>
       <c r="P98">
-        <v>-36.62052992</v>
+        <v>-37.02478544</v>
       </c>
       <c r="Q98">
-        <v>-34.68052992000001</v>
+        <v>-35.08478544</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.7624558373630971</v>
+        <v>1.00134111648413</v>
       </c>
       <c r="T98">
-        <v>13.96895618101538</v>
+        <v>18.62527490802051</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.01127587159065467</v>
+        <v>0.01115962549178194</v>
       </c>
       <c r="W98">
-        <v>0.2331411494789236</v>
+        <v>0.2331685603090378</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9349,7 +9349,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.05637935795327342</v>
+        <v>0.05579812745890977</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9357,22 +9357,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2562137369942906</v>
+        <v>0.2581137369942906</v>
       </c>
       <c r="C99">
-        <v>-172.3916514450063</v>
+        <v>-174.7892452504743</v>
       </c>
       <c r="D99">
-        <v>28.44934855499366</v>
+        <v>28.19475474952574</v>
       </c>
       <c r="E99">
-        <v>172.871</v>
+        <v>175.014</v>
       </c>
       <c r="F99">
-        <v>207.871</v>
+        <v>210.014</v>
       </c>
       <c r="G99">
         <v>7.03</v>
@@ -9393,37 +9393,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M99">
-        <v>49.01598180000001</v>
+        <v>49.5213012</v>
       </c>
       <c r="N99">
-        <v>-46.28098180000001</v>
+        <v>-46.7863012</v>
       </c>
       <c r="O99">
-        <v>-9.256196360000002</v>
+        <v>-9.35726024</v>
       </c>
       <c r="P99">
-        <v>-37.02478544</v>
+        <v>-37.42904096</v>
       </c>
       <c r="Q99">
-        <v>-35.08478544</v>
+        <v>-35.48904096</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.00134111648413</v>
+        <v>1.479111674726194</v>
       </c>
       <c r="T99">
-        <v>18.62527490802051</v>
+        <v>27.93791236203076</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.01115962549178194</v>
+        <v>0.01104575176227397</v>
       </c>
       <c r="W99">
-        <v>0.2331685603090378</v>
+        <v>0.2331954117344558</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9431,7 +9431,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.05579812745890977</v>
+        <v>0.05522875881136979</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9439,22 +9439,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2581137369942906</v>
+        <v>0.2600137369942906</v>
       </c>
       <c r="C100">
-        <v>-174.7892452504743</v>
+        <v>-177.1823227421224</v>
       </c>
       <c r="D100">
-        <v>28.19475474952574</v>
+        <v>27.94467725787765</v>
       </c>
       <c r="E100">
-        <v>175.014</v>
+        <v>177.157</v>
       </c>
       <c r="F100">
-        <v>210.014</v>
+        <v>212.157</v>
       </c>
       <c r="G100">
         <v>7.03</v>
@@ -9475,37 +9475,37 @@
         <v>2.734999999999999</v>
       </c>
       <c r="M100">
-        <v>49.5213012</v>
+        <v>50.0266206</v>
       </c>
       <c r="N100">
-        <v>-46.7863012</v>
+        <v>-47.2916206</v>
       </c>
       <c r="O100">
-        <v>-9.35726024</v>
+        <v>-9.45832412</v>
       </c>
       <c r="P100">
-        <v>-37.42904096</v>
+        <v>-37.83329648</v>
       </c>
       <c r="Q100">
-        <v>-35.48904096</v>
+        <v>-35.89329648</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.479111674726194</v>
+        <v>2.912423349452388</v>
       </c>
       <c r="T100">
-        <v>27.93791236203076</v>
+        <v>55.87582472406152</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.01104575176227397</v>
+        <v>0.01093417851214999</v>
       </c>
       <c r="W100">
-        <v>0.2331954117344558</v>
+        <v>0.2332217207068351</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9513,91 +9513,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.05522875881136979</v>
+        <v>0.05467089256074997</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2600137369942906</v>
-      </c>
-      <c r="C101">
-        <v>-177.1823227421224</v>
-      </c>
-      <c r="D101">
-        <v>27.94467725787765</v>
-      </c>
-      <c r="E101">
-        <v>177.157</v>
-      </c>
-      <c r="F101">
-        <v>212.157</v>
-      </c>
-      <c r="G101">
-        <v>7.03</v>
-      </c>
-      <c r="H101">
-        <v>179.3</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.675</v>
-      </c>
-      <c r="K101">
-        <v>1.94</v>
-      </c>
-      <c r="L101">
-        <v>2.734999999999999</v>
-      </c>
-      <c r="M101">
-        <v>50.0266206</v>
-      </c>
-      <c r="N101">
-        <v>-47.2916206</v>
-      </c>
-      <c r="O101">
-        <v>-9.45832412</v>
-      </c>
-      <c r="P101">
-        <v>-37.83329648</v>
-      </c>
-      <c r="Q101">
-        <v>-35.89329648</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.912423349452388</v>
-      </c>
-      <c r="T101">
-        <v>55.87582472406152</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.01093417851214999</v>
-      </c>
-      <c r="W101">
-        <v>0.2332217207068351</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.05467089256074997</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
